--- a/data/uploads/nykaa_ai_discovery_database_100_new_statements.xlsx
+++ b/data/uploads/nykaa_ai_discovery_database_100_new_statements.xlsx
@@ -16,8 +16,6 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Feedback_Raw'!$A$1:$R$111</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Taxonomy'!$A$1:$C$8</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'AI_Classification'!$A$1:$Q$11</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Opportunity_Scoring'!$A$1:$H$7</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'README'!$A$1:$B$6</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -5753,447 +5751,9227 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q11"/>
+  <dimension ref="A1:Q111"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="45" customWidth="1" min="3" max="3"/>
-    <col width="39" customWidth="1" min="4" max="4"/>
-    <col width="17" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="17" customWidth="1" min="7" max="7"/>
-    <col width="21" customWidth="1" min="8" max="8"/>
-    <col width="17" customWidth="1" min="9" max="9"/>
-    <col width="19" customWidth="1" min="10" max="10"/>
-    <col width="18" customWidth="1" min="11" max="11"/>
-    <col width="12" customWidth="1" min="12" max="12"/>
-    <col width="12" customWidth="1" min="13" max="13"/>
-    <col width="12" customWidth="1" min="14" max="14"/>
-    <col width="12" customWidth="1" min="15" max="15"/>
-    <col width="12" customWidth="1" min="16" max="16"/>
-    <col width="23" customWidth="1" min="17" max="17"/>
-  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="6" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>record_id</t>
         </is>
       </c>
-      <c r="B1" s="6" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>source</t>
         </is>
       </c>
-      <c r="C1" s="6" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>text</t>
         </is>
       </c>
-      <c r="D1" s="6" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>category</t>
         </is>
       </c>
-      <c r="E1" s="6" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>wishlist_intent</t>
         </is>
       </c>
-      <c r="F1" s="6" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>purchase_blocker</t>
         </is>
       </c>
-      <c r="G1" s="6" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>information_gap</t>
         </is>
       </c>
-      <c r="H1" s="6" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>comparison_behavior</t>
         </is>
       </c>
-      <c r="I1" s="6" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>comparison_type</t>
         </is>
       </c>
-      <c r="J1" s="6" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>external_research</t>
         </is>
       </c>
-      <c r="K1" s="6" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>decision_trigger</t>
         </is>
       </c>
-      <c r="L1" s="6" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>sentiment</t>
         </is>
       </c>
-      <c r="M1" s="6" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>confidence</t>
         </is>
       </c>
-      <c r="N1" s="6" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>evidence</t>
         </is>
       </c>
-      <c r="O1" s="6" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>theme</t>
         </is>
       </c>
-      <c r="P1" s="6" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>segment</t>
         </is>
       </c>
-      <c r="Q1" s="6" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>opportunity_relevance</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="4" t="n">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Survey</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>I want to remember the product, I like the product but am unsure about buying it | I forgot about it | No | Product price, Product quality | Keep comparing platforms | Current price, Price comparison with other platforms, Quality information | Socks</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Fashion (non-beauty)</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>COMPARISON</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>['COMPARISON']</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>['COMPARISON']</t>
+        </is>
+      </c>
+      <c r="H2" t="b">
         <v>1</v>
       </c>
-      <c r="B2" s="4" t="inlineStr">
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>['SIMILAR_PRODUCT']</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>['NONE']</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>['BETTER_ALTERNATIVE']</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M2" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>Product price</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>COMPARISON</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>FASHION_COMPARISON</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>COMPARISON</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
         <is>
           <t>Survey</t>
         </is>
       </c>
-      <c r="C2" s="4" t="inlineStr">
-        <is>
-          <t>I want to remember the product, I like the product but am unsure about buying it | I forgot about it | No | Product price, Product quality | Keep comparing platforms | Current price, Price comparison with other platforms, Quality information | Socks</t>
-        </is>
-      </c>
-      <c r="D2" s="4" t="inlineStr">
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>I want to compare it with other products, I like the product but am unsure about buying it | I found it cheaper elsewhere, I found a better alternative, I forgot about it | Yes, I checked the exact same product | Product price, Discounts/coupons, Bank/card offers, Delivery time, Return policy, Reviews/ratings, Product quality | Buy it from the cheaper platform, Decide not to purchase | Current price, Reviews, Quality information | Social Influence</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Exploratory fashion wishlist response</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>COMPARISON</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>['COMPARISON']</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>['COMPARISON']</t>
+        </is>
+      </c>
+      <c r="H3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>['SIMILAR_PRODUCT']</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>['NONE']</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>['BETTER_ALTERNATIVE']</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M3" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>I want to compare it with other products</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>COMPARISON</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>FASHION_COMPARISON</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>COMPARISON</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Survey</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>I intend to buy it later | I was waiting for a discount/offer | Yes, I checked similar products | Product price, Discounts/coupons, Shipping cost, Delivery time, Return policy, Reviews/ratings, Product quality | Wait for a sale, Look for a coupon/offer, Keep comparing platforms | Current price, Price comparison with other platforms, Expected future price/drop | The last item I really wanted was an Agnes Tachyon plushie from Uma Musume. As soon as I saw it online, I thought it looked really cute and added it to my wishlist so I wouldn't lose it.  After saving it, I kept checking the product page every few days. I looked at different sellers to compare prices, checked customer reviews and photos, and even watched a few unboxing videos to see the quality and size of the plushie. I also waited to see if there would be a discount or sale.  For a while, I seriously considered buying it and even added it to my cart once. But I eventually decided not to purchase it because it was a bit expensive, especially after shipping costs were added, and I wanted to save my money for more important expenses. I left it on my wishlist instead, hoping I might buy it later if the price drops or there's a good sale.</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Exploratory fashion wishlist response</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>COMPARISON</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>['COMPARISON']</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>['COMPARISON']</t>
+        </is>
+      </c>
+      <c r="H4" t="b">
+        <v>1</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>['SIMILAR_PRODUCT']</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>['NONE']</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>['BETTER_ALTERNATIVE']</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M4" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>I was waiting for a discount/offer</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>COMPARISON</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>FASHION_COMPARISON</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>COMPARISON</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Survey</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>I like the product but am unsure about buying it | I wasn't sure about the quality | Yes, I checked similar products | Product price, Delivery time, Product quality | Buy it from the cheaper platform | Price comparison with other platforms, Size/fit information, Quality information, Return policy | Co-ord Set, added to my wish list but the price was too much, but checked some other websites and found similar options less price.</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
         <is>
           <t>Fashion (non-beauty)</t>
         </is>
       </c>
-      <c r="E2" s="4" t="inlineStr"/>
-      <c r="F2" s="4" t="inlineStr"/>
-      <c r="G2" s="4" t="inlineStr"/>
-      <c r="H2" s="4" t="inlineStr"/>
-      <c r="I2" s="4" t="inlineStr"/>
-      <c r="J2" s="4" t="inlineStr"/>
-      <c r="K2" s="4" t="inlineStr"/>
-      <c r="L2" s="4" t="inlineStr"/>
-      <c r="M2" s="4" t="inlineStr"/>
-      <c r="N2" s="4" t="inlineStr"/>
-      <c r="O2" s="4" t="inlineStr"/>
-      <c r="P2" s="4" t="inlineStr"/>
-      <c r="Q2" s="4" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="B3" s="4" t="inlineStr">
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>WAITING_FOR_BETTER_VALUE</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>['SIZE_FORMAT']</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>['PRICE_VALUE']</t>
+        </is>
+      </c>
+      <c r="H5" t="b">
+        <v>0</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>['NONE']</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>['OTHER_MARKETPLACE']</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>['LOWER_PRICE']</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M5" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>Product price</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>PRICE_VALUE</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>FASHION_PRICE_VALUE</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>PRICE_VALUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
         <is>
           <t>Survey</t>
         </is>
       </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>I want to compare it with other products, I like the product but am unsure about buying it | I found it cheaper elsewhere, I found a better alternative, I forgot about it | Yes, I checked the exact same product | Product price, Discounts/coupons, Bank/card offers, Delivery time, Return policy, Reviews/ratings, Product quality | Buy it from the cheaper platform, Decide not to purchase | Current price, Reviews, Quality information | Social Influence</t>
-        </is>
-      </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>I like the product but am unsure about buying it | I forgot about it | I don't remember | Product price | Buy it from the cheaper platform | Current price, Reviews, Quality information</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
         <is>
           <t>Exploratory fashion wishlist response</t>
         </is>
       </c>
-      <c r="E3" s="4" t="inlineStr"/>
-      <c r="F3" s="4" t="inlineStr"/>
-      <c r="G3" s="4" t="inlineStr"/>
-      <c r="H3" s="4" t="inlineStr"/>
-      <c r="I3" s="4" t="inlineStr"/>
-      <c r="J3" s="4" t="inlineStr"/>
-      <c r="K3" s="4" t="inlineStr"/>
-      <c r="L3" s="4" t="inlineStr"/>
-      <c r="M3" s="4" t="inlineStr"/>
-      <c r="N3" s="4" t="inlineStr"/>
-      <c r="O3" s="4" t="inlineStr"/>
-      <c r="P3" s="4" t="inlineStr"/>
-      <c r="Q3" s="4" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="B4" s="4" t="inlineStr">
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>WAITING_FOR_BETTER_VALUE</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>['PRICE_VALUE']</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>['PRICE_VALUE']</t>
+        </is>
+      </c>
+      <c r="H6" t="b">
+        <v>0</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>['NONE']</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>['NONE']</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>['LOWER_PRICE']</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M6" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>Product price</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>PRICE_VALUE</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>FASHION_PRICE_VALUE</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>PRICE_VALUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
         <is>
           <t>Survey</t>
         </is>
       </c>
-      <c r="C4" s="4" t="inlineStr">
-        <is>
-          <t>I intend to buy it later | I was waiting for a discount/offer | Yes, I checked similar products | Product price, Discounts/coupons, Shipping cost, Delivery time, Return policy, Reviews/ratings, Product quality | Wait for a sale, Look for a coupon/offer, Keep comparing platforms | Current price, Price comparison with other platforms, Expected future price/drop | The last item I really wanted was an Agnes Tachyon plushie from Uma Musume. As soon as I saw it online, I thought it looked really cute and added it to my wishlist so I wouldn't lose it.  After saving it, I kept checking the product page every few days. I looked at different sellers to compare prices, checked customer reviews and photos, and even watched a few unboxing videos to see the quality and size of the plushie. I also waited to see if there would be a discount or sale.  For a while, I seriously considered buying it and even added it to my cart once. But I eventually decided not to purchase it because it was a bit expensive, especially after shipping costs were added, and I wanted to save my money for more important expenses. I left it on my wishlist instead, hoping I might buy it later if the price drops or there's a good sale.</t>
-        </is>
-      </c>
-      <c r="D4" s="4" t="inlineStr">
-        <is>
-          <t>Exploratory fashion wishlist response</t>
-        </is>
-      </c>
-      <c r="E4" s="4" t="inlineStr"/>
-      <c r="F4" s="4" t="inlineStr"/>
-      <c r="G4" s="4" t="inlineStr"/>
-      <c r="H4" s="4" t="inlineStr"/>
-      <c r="I4" s="4" t="inlineStr"/>
-      <c r="J4" s="4" t="inlineStr"/>
-      <c r="K4" s="4" t="inlineStr"/>
-      <c r="L4" s="4" t="inlineStr"/>
-      <c r="M4" s="4" t="inlineStr"/>
-      <c r="N4" s="4" t="inlineStr"/>
-      <c r="O4" s="4" t="inlineStr"/>
-      <c r="P4" s="4" t="inlineStr"/>
-      <c r="Q4" s="4" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="B5" s="4" t="inlineStr">
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>I intend to buy it later, I want to compare it with other products, I am waiting for a better price/offer, I want to remember the product, I am not ready to buy yet | I was waiting for a discount/offer | Yes, I checked similar products | Product price, Discounts/coupons, Bank/card offers, Cashback, Shipping cost, Delivery time, Return policy, Reviews/ratings | Buy it from the cheaper platform | Current price | shirt</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Fashion (non-beauty)</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>COMPARISON</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>['COMPARISON']</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>['COMPARISON']</t>
+        </is>
+      </c>
+      <c r="H7" t="b">
+        <v>1</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>['SIMILAR_PRODUCT']</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>['NONE']</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>['BETTER_ALTERNATIVE']</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M7" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>I want to compare it with other products</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>COMPARISON</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>FASHION_COMPARISON</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>COMPARISON</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
         <is>
           <t>Survey</t>
         </is>
       </c>
-      <c r="C5" s="4" t="inlineStr">
-        <is>
-          <t>I like the product but am unsure about buying it | I wasn't sure about the quality | Yes, I checked similar products | Product price, Delivery time, Product quality | Buy it from the cheaper platform | Price comparison with other platforms, Size/fit information, Quality information, Return policy | Co-ord Set, added to my wish list but the price was too much, but checked some other websites and found similar options less price.</t>
-        </is>
-      </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>I am waiting for a better price/offer, I want to remember the product | I was waiting for a discount/offer, I wasn't sure about the size/fit, I wasn't sure about the quality | Yes, I checked the exact same product | Product price, Shipping cost, Delivery time, Reviews/ratings | Buy it from the cheaper platform | Price comparison with other platforms, Expected future price/drop, Quality information | I saved a pair of Skechers shoes to my wishlist after comparing the design, price, reviews, and alternatives. I checked them again later and realized I didn’t need another pair right now, so I decided not to purchase them.</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
         <is>
           <t>Fashion (non-beauty)</t>
         </is>
       </c>
-      <c r="E5" s="4" t="inlineStr"/>
-      <c r="F5" s="4" t="inlineStr"/>
-      <c r="G5" s="4" t="inlineStr"/>
-      <c r="H5" s="4" t="inlineStr"/>
-      <c r="I5" s="4" t="inlineStr"/>
-      <c r="J5" s="4" t="inlineStr"/>
-      <c r="K5" s="4" t="inlineStr"/>
-      <c r="L5" s="4" t="inlineStr"/>
-      <c r="M5" s="4" t="inlineStr"/>
-      <c r="N5" s="4" t="inlineStr"/>
-      <c r="O5" s="4" t="inlineStr"/>
-      <c r="P5" s="4" t="inlineStr"/>
-      <c r="Q5" s="4" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="B6" s="4" t="inlineStr">
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>COMPARISON</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>['COMPARISON']</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>['COMPARISON']</t>
+        </is>
+      </c>
+      <c r="H8" t="b">
+        <v>1</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>['SIMILAR_PRODUCT']</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>['NONE']</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>['BETTER_ALTERNATIVE']</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M8" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>I am waiting for a better price/offer</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>COMPARISON</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>FASHION_COMPARISON</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>COMPARISON</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
         <is>
           <t>Survey</t>
         </is>
       </c>
-      <c r="C6" s="4" t="inlineStr">
-        <is>
-          <t>I like the product but am unsure about buying it | I forgot about it | I don't remember | Product price | Buy it from the cheaper platform | Current price, Reviews, Quality information</t>
-        </is>
-      </c>
-      <c r="D6" s="4" t="inlineStr">
-        <is>
-          <t>Exploratory fashion wishlist response</t>
-        </is>
-      </c>
-      <c r="E6" s="4" t="inlineStr"/>
-      <c r="F6" s="4" t="inlineStr"/>
-      <c r="G6" s="4" t="inlineStr"/>
-      <c r="H6" s="4" t="inlineStr"/>
-      <c r="I6" s="4" t="inlineStr"/>
-      <c r="J6" s="4" t="inlineStr"/>
-      <c r="K6" s="4" t="inlineStr"/>
-      <c r="L6" s="4" t="inlineStr"/>
-      <c r="M6" s="4" t="inlineStr"/>
-      <c r="N6" s="4" t="inlineStr"/>
-      <c r="O6" s="4" t="inlineStr"/>
-      <c r="P6" s="4" t="inlineStr"/>
-      <c r="Q6" s="4" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="B7" s="4" t="inlineStr">
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>I am waiting for a better price/offer | I found a better alternative | Yes, I checked the exact same product | Discounts/coupons, Delivery time | Buy it from the cheaper platform | Price comparison with other platforms | Snitch Jacket</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Fashion (non-beauty)</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>WAITING_FOR_BETTER_VALUE</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>['PRICE_VALUE']</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>['PRICE_VALUE']</t>
+        </is>
+      </c>
+      <c r="H9" t="b">
+        <v>0</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>['NONE']</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>['NONE']</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>['LOWER_PRICE']</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M9" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>I am waiting for a better price/offer</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>PRICE_VALUE</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>FASHION_PRICE_VALUE</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>PRICE_VALUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
         <is>
           <t>Survey</t>
         </is>
       </c>
-      <c r="C7" s="4" t="inlineStr">
-        <is>
-          <t>I intend to buy it later, I want to compare it with other products, I am waiting for a better price/offer, I want to remember the product, I am not ready to buy yet | I was waiting for a discount/offer | Yes, I checked similar products | Product price, Discounts/coupons, Bank/card offers, Cashback, Shipping cost, Delivery time, Return policy, Reviews/ratings | Buy it from the cheaper platform | Current price | shirt</t>
-        </is>
-      </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>I want to compare it with other products, I like the product but am unsure about buying it | I was waiting for a discount/offer | Yes, I checked similar products | Product price, Delivery time, Return policy | Buy it from the cheaper platform | Available offers for me, Reviews, Size/fit information, Return policy | The last fashionable thing I wanted to buy was a new jacket. I found it on the marketplace. But I refused to buy it for several reasons: long delivery, lack of size range and reviews</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
         <is>
           <t>Fashion (non-beauty)</t>
         </is>
       </c>
-      <c r="E7" s="4" t="inlineStr"/>
-      <c r="F7" s="4" t="inlineStr"/>
-      <c r="G7" s="4" t="inlineStr"/>
-      <c r="H7" s="4" t="inlineStr"/>
-      <c r="I7" s="4" t="inlineStr"/>
-      <c r="J7" s="4" t="inlineStr"/>
-      <c r="K7" s="4" t="inlineStr"/>
-      <c r="L7" s="4" t="inlineStr"/>
-      <c r="M7" s="4" t="inlineStr"/>
-      <c r="N7" s="4" t="inlineStr"/>
-      <c r="O7" s="4" t="inlineStr"/>
-      <c r="P7" s="4" t="inlineStr"/>
-      <c r="Q7" s="4" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="4" t="n">
-        <v>7</v>
-      </c>
-      <c r="B8" s="4" t="inlineStr">
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>COMPARISON</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>['COMPARISON']</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>['COMPARISON']</t>
+        </is>
+      </c>
+      <c r="H10" t="b">
+        <v>1</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>['SIMILAR_PRODUCT']</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>['OTHER_MARKETPLACE']</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>['BETTER_ALTERNATIVE']</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M10" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>I want to compare it with other products</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>COMPARISON</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>FASHION_COMPARISON</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>COMPARISON</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
         <is>
           <t>Survey</t>
         </is>
       </c>
-      <c r="C8" s="4" t="inlineStr">
-        <is>
-          <t>I am waiting for a better price/offer, I want to remember the product | I was waiting for a discount/offer, I wasn't sure about the size/fit, I wasn't sure about the quality | Yes, I checked the exact same product | Product price, Shipping cost, Delivery time, Reviews/ratings | Buy it from the cheaper platform | Price comparison with other platforms, Expected future price/drop, Quality information | I saved a pair of Skechers shoes to my wishlist after comparing the design, price, reviews, and alternatives. I checked them again later and realized I didn’t need another pair right now, so I decided not to purchase them.</t>
-        </is>
-      </c>
-      <c r="D8" s="4" t="inlineStr">
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>I intend to buy it later | I was waiting for a discount/offer | Yes, I checked the exact same product | Product price, Discounts/coupons | Buy it from the cheaper platform, Keep comparing platforms | Price comparison with other platforms, Available offers for me, Reviews | T shirts I liked</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
         <is>
           <t>Fashion (non-beauty)</t>
         </is>
       </c>
-      <c r="E8" s="4" t="inlineStr"/>
-      <c r="F8" s="4" t="inlineStr"/>
-      <c r="G8" s="4" t="inlineStr"/>
-      <c r="H8" s="4" t="inlineStr"/>
-      <c r="I8" s="4" t="inlineStr"/>
-      <c r="J8" s="4" t="inlineStr"/>
-      <c r="K8" s="4" t="inlineStr"/>
-      <c r="L8" s="4" t="inlineStr"/>
-      <c r="M8" s="4" t="inlineStr"/>
-      <c r="N8" s="4" t="inlineStr"/>
-      <c r="O8" s="4" t="inlineStr"/>
-      <c r="P8" s="4" t="inlineStr"/>
-      <c r="Q8" s="4" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="B9" s="4" t="inlineStr">
-        <is>
-          <t>Survey</t>
-        </is>
-      </c>
-      <c r="C9" s="4" t="inlineStr">
-        <is>
-          <t>I am waiting for a better price/offer | I found a better alternative | Yes, I checked the exact same product | Discounts/coupons, Delivery time | Buy it from the cheaper platform | Price comparison with other platforms | Snitch Jacket</t>
-        </is>
-      </c>
-      <c r="D9" s="4" t="inlineStr">
-        <is>
-          <t>Fashion (non-beauty)</t>
-        </is>
-      </c>
-      <c r="E9" s="4" t="inlineStr"/>
-      <c r="F9" s="4" t="inlineStr"/>
-      <c r="G9" s="4" t="inlineStr"/>
-      <c r="H9" s="4" t="inlineStr"/>
-      <c r="I9" s="4" t="inlineStr"/>
-      <c r="J9" s="4" t="inlineStr"/>
-      <c r="K9" s="4" t="inlineStr"/>
-      <c r="L9" s="4" t="inlineStr"/>
-      <c r="M9" s="4" t="inlineStr"/>
-      <c r="N9" s="4" t="inlineStr"/>
-      <c r="O9" s="4" t="inlineStr"/>
-      <c r="P9" s="4" t="inlineStr"/>
-      <c r="Q9" s="4" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="4" t="n">
-        <v>9</v>
-      </c>
-      <c r="B10" s="4" t="inlineStr">
-        <is>
-          <t>Survey</t>
-        </is>
-      </c>
-      <c r="C10" s="4" t="inlineStr">
-        <is>
-          <t>I want to compare it with other products, I like the product but am unsure about buying it | I was waiting for a discount/offer | Yes, I checked similar products | Product price, Delivery time, Return policy | Buy it from the cheaper platform | Available offers for me, Reviews, Size/fit information, Return policy | The last fashionable thing I wanted to buy was a new jacket. I found it on the marketplace. But I refused to buy it for several reasons: long delivery, lack of size range and reviews</t>
-        </is>
-      </c>
-      <c r="D10" s="4" t="inlineStr">
-        <is>
-          <t>Fashion (non-beauty)</t>
-        </is>
-      </c>
-      <c r="E10" s="4" t="inlineStr"/>
-      <c r="F10" s="4" t="inlineStr"/>
-      <c r="G10" s="4" t="inlineStr"/>
-      <c r="H10" s="4" t="inlineStr"/>
-      <c r="I10" s="4" t="inlineStr"/>
-      <c r="J10" s="4" t="inlineStr"/>
-      <c r="K10" s="4" t="inlineStr"/>
-      <c r="L10" s="4" t="inlineStr"/>
-      <c r="M10" s="4" t="inlineStr"/>
-      <c r="N10" s="4" t="inlineStr"/>
-      <c r="O10" s="4" t="inlineStr"/>
-      <c r="P10" s="4" t="inlineStr"/>
-      <c r="Q10" s="4" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="B11" s="4" t="inlineStr">
-        <is>
-          <t>Survey</t>
-        </is>
-      </c>
-      <c r="C11" s="4" t="inlineStr">
-        <is>
-          <t>I intend to buy it later | I was waiting for a discount/offer | Yes, I checked the exact same product | Product price, Discounts/coupons | Buy it from the cheaper platform, Keep comparing platforms | Price comparison with other platforms, Available offers for me, Reviews | T shirts I liked</t>
-        </is>
-      </c>
-      <c r="D11" s="4" t="inlineStr">
-        <is>
-          <t>Fashion (non-beauty)</t>
-        </is>
-      </c>
-      <c r="E11" s="4" t="inlineStr"/>
-      <c r="F11" s="4" t="inlineStr"/>
-      <c r="G11" s="4" t="inlineStr"/>
-      <c r="H11" s="4" t="inlineStr"/>
-      <c r="I11" s="4" t="inlineStr"/>
-      <c r="J11" s="4" t="inlineStr"/>
-      <c r="K11" s="4" t="inlineStr"/>
-      <c r="L11" s="4" t="inlineStr"/>
-      <c r="M11" s="4" t="inlineStr"/>
-      <c r="N11" s="4" t="inlineStr"/>
-      <c r="O11" s="4" t="inlineStr"/>
-      <c r="P11" s="4" t="inlineStr"/>
-      <c r="Q11" s="4" t="inlineStr"/>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>COMPARISON</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>['COMPARISON']</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>['COMPARISON']</t>
+        </is>
+      </c>
+      <c r="H11" t="b">
+        <v>1</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>['SIMILAR_PRODUCT']</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>['NONE']</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>['BETTER_ALTERNATIVE']</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M11" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>I was waiting for a discount/offer</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>COMPARISON</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>FASHION_COMPARISON</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>COMPARISON</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>NEW001</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Synthetic Test</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>I keep going back to this lipstick because the colour looks perfect in photos, but I want to know whether it appears deeper on medium skin.</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Lipstick</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>GENUINE_PURCHASE_INTENT</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>['SHADE']</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>['SHADE_CONFIDENCE']</t>
+        </is>
+      </c>
+      <c r="H12" t="b">
+        <v>0</v>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>['NONE']</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>['NONE']</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>['SHADE_CONFIRMATION']</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M12" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>but I want to know whether it appears deeper on medium skin</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>SHADE_CONFIDENCE</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>LIPSTICK_SHADE_CONFIDENCE</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>SHADE_CONFIDENCE</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>NEW002</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Synthetic Test</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>The shade is tempting, although I usually prefer a softer finish. I am checking if this range has something similar in satin.</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Lipstick</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>GENUINE_PURCHASE_INTENT</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>['SHADE']</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>['SHADE_CONFIDENCE']</t>
+        </is>
+      </c>
+      <c r="H13" t="b">
+        <v>0</v>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>['NONE']</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>['NONE']</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>['SHADE_CONFIRMATION']</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M13" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>The shade is tempting</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>SHADE_CONFIDENCE</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>LIPSTICK_SHADE_CONFIDENCE</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>SHADE_CONFIDENCE</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>NEW003</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Synthetic Test</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>I know the brand works for me, but I am between two foundation shades and don't want to guess from a tiny swatch.</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Foundation</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>GENUINE_PURCHASE_INTENT</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>['SHADE']</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>['SHADE_CONFIDENCE']</t>
+        </is>
+      </c>
+      <c r="H14" t="b">
+        <v>0</v>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>['NONE']</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>['NONE']</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>['SHADE_CONFIRMATION']</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M14" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>but I am between two foundation shades and don't want to guess from a tiny swatch</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>SHADE_CONFIDENCE</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>FOUNDATION_SHADE_CONFIDENCE</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>SHADE_CONFIDENCE</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>NEW004</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Synthetic Test</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>The coverage is exactly what I want; the hesitation is whether it will separate around my nose during a long day.</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Foundation</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>GENUINE_PURCHASE_INTENT</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>['OTHER']</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>['PRICE_VALUE']</t>
+        </is>
+      </c>
+      <c r="H15" t="b">
+        <v>0</v>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>['NONE']</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>['NONE']</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>['LOWER_PRICE']</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M15" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>The coverage is exactly what I want</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>PRICE_VALUE</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>FOUNDATION_PRICE_VALUE</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>PRICE_VALUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>NEW005</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Synthetic Test</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>I saved this after a creator recommended it, then started comparing how it photographs under different lighting.</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Foundation</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>COMPARISON</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>['COMPARISON']</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>['COMPARISON']</t>
+        </is>
+      </c>
+      <c r="H16" t="b">
+        <v>1</v>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>['SIMILAR_PRODUCT']</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>['NONE']</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>['BETTER_ALTERNATIVE']</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M16" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>I saved this after a creator recommended it</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>COMPARISON</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>FOUNDATION_COMPARISON</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>COMPARISON</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>NEW006</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Synthetic Test</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>I like the concealer, but I need something that won't crease when I wear it for eight hours.</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Concealer</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>WAITING_FOR_BETTER_VALUE</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>['PRICE_VALUE']</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>['PRICE_VALUE']</t>
+        </is>
+      </c>
+      <c r="H17" t="b">
+        <v>0</v>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>['NONE']</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>['NONE']</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>['LOWER_PRICE']</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M17" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>but I need something that won't crease when I wear it for eight hours</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>PRICE_VALUE</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>CONCEALER_PRICE_VALUE</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>PRICE_VALUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>NEW007</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Synthetic Test</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>The shade looks right on the model, yet I'm unsure if it will be too yellow compared with my current foundation.</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Concealer</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>COMPARISON</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>['COMPARISON']</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>['COMPARISON']</t>
+        </is>
+      </c>
+      <c r="H18" t="b">
+        <v>1</v>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>['SIMILAR_PRODUCT']</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>['NONE']</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>['BETTER_ALTERNATIVE']</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M18" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>The shade looks right on the model</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>COMPARISON</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>CONCEALER_COMPARISON</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>COMPARISON</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>NEW008</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Synthetic Test</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>I want the peachy tone, but I'm nervous that the shimmer will be too visible in daylight.</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Blush</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>GENUINE_PURCHASE_INTENT</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>['SHADE']</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>['SHADE_CONFIDENCE']</t>
+        </is>
+      </c>
+      <c r="H19" t="b">
+        <v>0</v>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>['NONE']</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>['NONE']</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>['SHADE_CONFIRMATION']</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M19" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>I want the peachy tone</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>SHADE_CONFIDENCE</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>BLUSH_SHADE_CONFIDENCE</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>SHADE_CONFIDENCE</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>NEW009</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Synthetic Test</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>The blush is in my wishlist mainly because I can't decide between this coral and a similar muted pink.</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Blush</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>GENUINE_PURCHASE_INTENT</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>['OTHER']</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>['PRICE_VALUE']</t>
+        </is>
+      </c>
+      <c r="H20" t="b">
+        <v>0</v>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>['NONE']</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>['NONE']</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>['LOWER_PRICE']</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M20" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>The blush is in my wishlist mainly because I can't decide between this coral and a similar muted pink</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>PRICE_VALUE</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>BLUSH_PRICE_VALUE</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>PRICE_VALUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>NEW010</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Synthetic Test</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>I'm tempted by the volume claims, but clumping is a deal-breaker for me.</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Mascara</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>GENUINE_PURCHASE_INTENT</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>['OTHER']</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>['PRICE_VALUE']</t>
+        </is>
+      </c>
+      <c r="H21" t="b">
+        <v>0</v>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>['NONE']</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>['NONE']</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>['LOWER_PRICE']</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M21" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>I'm tempted by the volume claims</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>PRICE_VALUE</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>MASCARA_PRICE_VALUE</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>PRICE_VALUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>NEW011</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Synthetic Test</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>I bookmarked this mascara after seeing the brush, then wondered whether it smudges by evening.</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Mascara</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>GENUINE_PURCHASE_INTENT</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>['PERFORMANCE_DOUBT']</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>['PRODUCT_QUALITY']</t>
+        </is>
+      </c>
+      <c r="H22" t="b">
+        <v>0</v>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>['NONE']</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>['NONE']</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>['PRODUCT_DEMO']</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M22" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>I bookmarked this mascara after seeing the brush</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>QUALITY_TRUST</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>MASCARA_QUALITY_TRUST</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>QUALITY_TRUST</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>NEW012</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Synthetic Test</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>The gloss looks pretty, but I prefer a formula that doesn't leave my hair stuck to my lips.</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Lip Gloss</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>GENUINE_PURCHASE_INTENT</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>['OTHER']</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>['PRICE_VALUE']</t>
+        </is>
+      </c>
+      <c r="H23" t="b">
+        <v>0</v>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>['NONE']</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>['NONE']</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>['LOWER_PRICE']</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M23" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>The gloss looks pretty</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>PRICE_VALUE</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>LIP_GLOSS_PRICE_VALUE</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>PRICE_VALUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>NEW013</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Synthetic Test</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>I keep checking this gloss because the shine is right, although I'd choose a less sheer colour.</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Lip Gloss</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>GENUINE_PURCHASE_INTENT</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>['SHADE']</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>['SHADE_CONFIDENCE']</t>
+        </is>
+      </c>
+      <c r="H24" t="b">
+        <v>0</v>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>['NONE']</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>['NONE']</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>['SHADE_CONFIRMATION']</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M24" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>I keep checking this gloss because the shine is right</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>SHADE_CONFIDENCE</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>LIP_GLOSS_SHADE_CONFIDENCE</t>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>SHADE_CONFIDENCE</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>NEW014</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Synthetic Test</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>This serum is on my wishlist while I compare whether its ingredients make more sense for my current routine.</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Serum</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>COMPARISON</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>['COMPARISON']</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>['COMPARISON']</t>
+        </is>
+      </c>
+      <c r="H25" t="b">
+        <v>1</v>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>['SIMILAR_PRODUCT']</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>['NONE']</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>['BETTER_ALTERNATIVE']</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M25" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>This serum is on my wishlist while I compare whether its ingredients make more sense for my current routine</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>COMPARISON</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>SERUM_COMPARISON</t>
+        </is>
+      </c>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>COMPARISON</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>NEW015</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Synthetic Test</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>I saw good results in a few reviews, but I don't want to add another active without understanding what it pairs well with.</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Serum</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>WAITING_FOR_BETTER_VALUE</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>['PRICE_VALUE']</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>['PRICE_VALUE']</t>
+        </is>
+      </c>
+      <c r="H26" t="b">
+        <v>0</v>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>['NONE']</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>['NONE']</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>['LOWER_PRICE']</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M26" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>I saw good results in a few reviews</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>PRICE_VALUE</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>SERUM_PRICE_VALUE</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>PRICE_VALUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>NEW016</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Synthetic Test</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>The texture looks promising, but I want to know whether it pills when layered under makeup.</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Sunscreen</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>GENUINE_PURCHASE_INTENT</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>['SUITABILITY']</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>['SUITABILITY']</t>
+        </is>
+      </c>
+      <c r="H27" t="b">
+        <v>0</v>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>['NONE']</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>['NONE']</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>['SUITABILITY_CONFIDENCE']</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M27" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>The texture looks promising</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>SUITABILITY</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>SUNSCREEN_SUITABILITY</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>SUITABILITY</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>NEW017</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Synthetic Test</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>I saved this sunscreen because the finish seems invisible; I am still unsure about reapplication during the day.</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Sunscreen</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>GENUINE_PURCHASE_INTENT</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>['OTHER']</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>['PRICE_VALUE']</t>
+        </is>
+      </c>
+      <c r="H28" t="b">
+        <v>0</v>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>['NONE']</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>['NONE']</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>['LOWER_PRICE']</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M28" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>I saved this sunscreen because the finish seems invisible</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>PRICE_VALUE</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>SUNSCREEN_PRICE_VALUE</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>PRICE_VALUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>NEW018</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Synthetic Test</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>This moisturizer looks ideal for winter, but I need to decide if it will be too heavy once the weather gets warmer.</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Skincare</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>GENUINE_PURCHASE_INTENT</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>['OTHER']</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>['PRICE_VALUE']</t>
+        </is>
+      </c>
+      <c r="H29" t="b">
+        <v>0</v>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>['NONE']</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>['NONE']</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>['LOWER_PRICE']</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M29" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>This moisturizer looks ideal for winter</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>PRICE_VALUE</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>SKINCARE_PRICE_VALUE</t>
+        </is>
+      </c>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>PRICE_VALUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>NEW019</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Synthetic Test</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>I like the product concept, but I am checking whether the ingredients overlap with something I already own.</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Skincare</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>BOOKMARK</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>['NO_NEED']</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>['OTHER']</t>
+        </is>
+      </c>
+      <c r="H30" t="b">
+        <v>0</v>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>['NONE']</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>['NONE']</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>['BETTER_REVIEWS']</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M30" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>I like the product concept</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>INTENT_DECAY</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>SKINCARE_INTENT_DECAY</t>
+        </is>
+      </c>
+      <c r="Q30" t="inlineStr">
+        <is>
+          <t>INTENT_DECAY</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>NEW020</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Synthetic Test</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>I love the colour name, but I need to see the shade on deeper skin before choosing it.</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Lipstick</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>GENUINE_PURCHASE_INTENT</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>['SHADE']</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>['SHADE_CONFIDENCE']</t>
+        </is>
+      </c>
+      <c r="H31" t="b">
+        <v>0</v>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>['NONE']</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>['NONE']</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>['SHADE_CONFIRMATION']</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M31" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>but I need to see the shade on deeper skin before choosing it</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>SHADE_CONFIDENCE</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>LIPSTICK_SHADE_CONFIDENCE</t>
+        </is>
+      </c>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t>SHADE_CONFIDENCE</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>NEW021</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Synthetic Test</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>The price feels acceptable, yet I am undecided because another foundation has a finish I prefer.</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Foundation</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>WAITING_FOR_BETTER_VALUE</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>['PRICE_VALUE']</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>['PRICE_VALUE']</t>
+        </is>
+      </c>
+      <c r="H32" t="b">
+        <v>0</v>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>['NONE']</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>['NONE']</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>['LOWER_PRICE']</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M32" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>The price feels acceptable</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>PRICE_VALUE</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>FOUNDATION_PRICE_VALUE</t>
+        </is>
+      </c>
+      <c r="Q32" t="inlineStr">
+        <is>
+          <t>PRICE_VALUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>NEW022</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Synthetic Test</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>I would buy this if I knew whether it works better for dark circles than blemish coverage.</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Concealer</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>GENUINE_PURCHASE_INTENT</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>['OTHER']</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>['PRICE_VALUE']</t>
+        </is>
+      </c>
+      <c r="H33" t="b">
+        <v>0</v>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>['NONE']</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>['NONE']</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>['LOWER_PRICE']</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M33" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>I would buy this if I knew whether it works better for dark circles than blemish coverage</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>PRICE_VALUE</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>CONCEALER_PRICE_VALUE</t>
+        </is>
+      </c>
+      <c r="Q33" t="inlineStr">
+        <is>
+          <t>PRICE_VALUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>NEW023</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Synthetic Test</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>The shade is close to what I want, but I am unsure whether the pigment will be buildable or immediately intense.</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Blush</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>GENUINE_PURCHASE_INTENT</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>['SHADE']</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>['SHADE_CONFIDENCE']</t>
+        </is>
+      </c>
+      <c r="H34" t="b">
+        <v>0</v>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>['NONE']</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>['NONE']</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>['SHADE_CONFIRMATION']</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M34" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>The shade is close to what I want</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>SHADE_CONFIDENCE</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>BLUSH_SHADE_CONFIDENCE</t>
+        </is>
+      </c>
+      <c r="Q34" t="inlineStr">
+        <is>
+          <t>SHADE_CONFIDENCE</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>NEW024</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Synthetic Test</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>I keep comparing waterproof options because I need something for humid weather.</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Mascara</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>COMPARISON</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>['COMPARISON']</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>['COMPARISON']</t>
+        </is>
+      </c>
+      <c r="H35" t="b">
+        <v>1</v>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>['SIMILAR_PRODUCT']</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>['NONE']</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>['BETTER_ALTERNATIVE']</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M35" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>I keep comparing waterproof options because I need something for humid weather</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>COMPARISON</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>MASCARA_COMPARISON</t>
+        </is>
+      </c>
+      <c r="Q35" t="inlineStr">
+        <is>
+          <t>COMPARISON</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>NEW025</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Synthetic Test</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>I can't tell from the product photos whether this is glassy or just slightly glossy.</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Lip Gloss</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>GENUINE_PURCHASE_INTENT</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>['OTHER']</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>['PRICE_VALUE']</t>
+        </is>
+      </c>
+      <c r="H36" t="b">
+        <v>0</v>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>['NONE']</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>['NONE']</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>['LOWER_PRICE']</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M36" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>I can't tell from the product photos whether this is glassy or just slightly glossy</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>PRICE_VALUE</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>LIP_GLOSS_PRICE_VALUE</t>
+        </is>
+      </c>
+      <c r="Q36" t="inlineStr">
+        <is>
+          <t>PRICE_VALUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>NEW026</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Synthetic Test</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>The reviews are mixed on texture, so I'm looking for a lighter-feeling alternative with the same main benefit.</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Serum</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>GENUINE_PURCHASE_INTENT</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>['OTHER']</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>['PRICE_VALUE']</t>
+        </is>
+      </c>
+      <c r="H37" t="b">
+        <v>0</v>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>['NONE']</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>['NONE']</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>['LOWER_PRICE']</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M37" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>The reviews are mixed on texture</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>PRICE_VALUE</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>SERUM_PRICE_VALUE</t>
+        </is>
+      </c>
+      <c r="Q37" t="inlineStr">
+        <is>
+          <t>PRICE_VALUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>NEW027</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Synthetic Test</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>I prefer a natural finish and I'm checking whether this leaves enough glow without feeling greasy.</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Sunscreen</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>GENUINE_PURCHASE_INTENT</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>['OTHER']</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>['PRICE_VALUE']</t>
+        </is>
+      </c>
+      <c r="H38" t="b">
+        <v>0</v>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>['NONE']</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>['NONE']</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>['LOWER_PRICE']</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M38" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>I prefer a natural finish and I'm checking whether this leaves enough glow without feeling greasy</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>PRICE_VALUE</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>SUNSCREEN_PRICE_VALUE</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>PRICE_VALUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>NEW028</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Synthetic Test</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>I bookmarked this cleanser, but I want to know if it feels stripping after repeated use.</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Skincare</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>GENUINE_PURCHASE_INTENT</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>['SUITABILITY']</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>['SUITABILITY']</t>
+        </is>
+      </c>
+      <c r="H39" t="b">
+        <v>0</v>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>['NONE']</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>['NONE']</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>['SUITABILITY_CONFIDENCE']</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M39" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>I bookmarked this cleanser</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>SUITABILITY</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>SKINCARE_SUITABILITY</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>SUITABILITY</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>NEW029</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Synthetic Test</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>The original shade is beautiful, though I am searching for the same undertone in a slightly more wearable colour.</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Lipstick</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>GENUINE_PURCHASE_INTENT</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>['SHADE']</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>['SHADE_CONFIDENCE']</t>
+        </is>
+      </c>
+      <c r="H40" t="b">
+        <v>0</v>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>['NONE']</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>['NONE']</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>['SHADE_CONFIRMATION']</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M40" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>The original shade is beautiful</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>SHADE_CONFIDENCE</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>LIPSTICK_SHADE_CONFIDENCE</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>SHADE_CONFIDENCE</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>NEW030</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Synthetic Test</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>I am comparing this with a skin tint because I don't always want full coverage.</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Foundation</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>COMPARISON</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>['COMPARISON']</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>['COMPARISON']</t>
+        </is>
+      </c>
+      <c r="H41" t="b">
+        <v>1</v>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>['SIMILAR_PRODUCT']</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>['NONE']</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>['BETTER_ALTERNATIVE']</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M41" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>I am comparing this with a skin tint because I don't always want full coverage</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>COMPARISON</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>FOUNDATION_COMPARISON</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>COMPARISON</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>NEW031</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Synthetic Test</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>I need something that brightens without looking noticeably lighter than the rest of my face.</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Concealer</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>GENUINE_PURCHASE_INTENT</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>['OTHER']</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>['PRICE_VALUE']</t>
+        </is>
+      </c>
+      <c r="H42" t="b">
+        <v>0</v>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>['NONE']</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>['NONE']</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>['LOWER_PRICE']</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M42" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>I need something that brightens without looking noticeably lighter than the rest of my face</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>PRICE_VALUE</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>CONCEALER_PRICE_VALUE</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>PRICE_VALUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>NEW032</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Synthetic Test</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>The product looks promising, but I want to know how it blends over liquid foundation.</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Blush</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>GENUINE_PURCHASE_INTENT</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>['OTHER']</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>['PRICE_VALUE']</t>
+        </is>
+      </c>
+      <c r="H43" t="b">
+        <v>0</v>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>['NONE']</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>['NONE']</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>['LOWER_PRICE']</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M43" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>The product looks promising</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>PRICE_VALUE</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>BLUSH_PRICE_VALUE</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>PRICE_VALUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>NEW033</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Synthetic Test</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Length matters more to me than volume, so I am comparing the brush shape with a few lengthening formulas.</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Mascara</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>COMPARISON</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>['COMPARISON']</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>['COMPARISON']</t>
+        </is>
+      </c>
+      <c r="H44" t="b">
+        <v>1</v>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>['SIMILAR_PRODUCT']</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>['NONE']</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>['BETTER_ALTERNATIVE']</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M44" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>Length matters more to me than volume</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>COMPARISON</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>MASCARA_COMPARISON</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>COMPARISON</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>NEW034</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Synthetic Test</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>I'm interested in the plumping effect, but I want to know how strong the tingling feels.</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Lip Gloss</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>GENUINE_PURCHASE_INTENT</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>['OTHER']</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>['PRICE_VALUE']</t>
+        </is>
+      </c>
+      <c r="H45" t="b">
+        <v>0</v>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>['NONE']</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>['NONE']</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>['LOWER_PRICE']</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M45" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>I'm interested in the plumping effect</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>PRICE_VALUE</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>LIP_GLOSS_PRICE_VALUE</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>PRICE_VALUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>NEW035</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Synthetic Test</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>I saved this because of the ingredient list, but I am unsure whether the concentration is enough to justify switching.</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Serum</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>GENUINE_PURCHASE_INTENT</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>['OTHER']</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>['PRICE_VALUE']</t>
+        </is>
+      </c>
+      <c r="H46" t="b">
+        <v>0</v>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>['NONE']</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>['NONE']</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>['LOWER_PRICE']</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M46" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>I saved this because of the ingredient list</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>PRICE_VALUE</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>SERUM_PRICE_VALUE</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>PRICE_VALUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>NEW036</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Synthetic Test</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>The SPF is right for me; my remaining question is whether the formula leaves a cast around the hairline.</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Sunscreen</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>GENUINE_PURCHASE_INTENT</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>['OTHER']</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>['PRICE_VALUE']</t>
+        </is>
+      </c>
+      <c r="H47" t="b">
+        <v>0</v>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>['NONE']</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>['NONE']</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>['LOWER_PRICE']</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M47" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>The SPF is right for me</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>PRICE_VALUE</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>SUNSCREEN_PRICE_VALUE</t>
+        </is>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>PRICE_VALUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>NEW037</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Synthetic Test</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>I am looking for something soothing, and this seems close, but I need to know whether the fragrance is noticeable.</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Skincare</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>GENUINE_PURCHASE_INTENT</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>['INGREDIENT_SAFETY']</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>['SUITABILITY']</t>
+        </is>
+      </c>
+      <c r="H48" t="b">
+        <v>0</v>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>['NONE']</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>['NONE']</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>['SUITABILITY_CONFIDENCE']</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M48" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>I am looking for something soothing</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>SUITABILITY</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>SKINCARE_SUITABILITY</t>
+        </is>
+      </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>SUITABILITY</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>NEW038</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Synthetic Test</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>I had almost decided to buy it, then saw another lipstick with a similar tone and longer wear claims.</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Lipstick</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>GENUINE_PURCHASE_INTENT</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>['OTHER']</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>['PRICE_VALUE']</t>
+        </is>
+      </c>
+      <c r="H49" t="b">
+        <v>0</v>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>['NONE']</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>['NONE']</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>['LOWER_PRICE']</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M49" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>I had almost decided to buy it</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>PRICE_VALUE</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>LIPSTICK_PRICE_VALUE</t>
+        </is>
+      </c>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>PRICE_VALUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>NEW039</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Synthetic Test</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>I keep opening this product page because I like the finish, but I'm worried it will oxidize during the day.</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Foundation</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>GENUINE_PURCHASE_INTENT</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>['OTHER']</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>['PRICE_VALUE']</t>
+        </is>
+      </c>
+      <c r="H50" t="b">
+        <v>0</v>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>['NONE']</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>['NONE']</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>['LOWER_PRICE']</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M50" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>I keep opening this product page because I like the finish</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>PRICE_VALUE</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>FOUNDATION_PRICE_VALUE</t>
+        </is>
+      </c>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>PRICE_VALUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>NEW040</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Synthetic Test</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>The coverage looks good, although I am concerned it might emphasize fine lines.</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Concealer</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>GENUINE_PURCHASE_INTENT</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>['OTHER']</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>['PRICE_VALUE']</t>
+        </is>
+      </c>
+      <c r="H51" t="b">
+        <v>0</v>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>['NONE']</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>['NONE']</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>['LOWER_PRICE']</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M51" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>The coverage looks good</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>PRICE_VALUE</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>CONCEALER_PRICE_VALUE</t>
+        </is>
+      </c>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>PRICE_VALUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>NEW041</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Synthetic Test</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>I want a blush that works for both everyday and evening makeup, so I'm weighing this shade against a deeper one.</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Blush</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>GENUINE_PURCHASE_INTENT</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>['SHADE']</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>['SHADE_CONFIDENCE']</t>
+        </is>
+      </c>
+      <c r="H52" t="b">
+        <v>0</v>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>['NONE']</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>['NONE']</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>['SHADE_CONFIRMATION']</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M52" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>so I'm weighing this shade against a deeper one</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>SHADE_CONFIDENCE</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>BLUSH_SHADE_CONFIDENCE</t>
+        </is>
+      </c>
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t>SHADE_CONFIDENCE</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>NEW042</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Synthetic Test</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>I saved this after a friend suggested it, but the small brush makes me wonder if application will take too long.</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Mascara</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>GENUINE_PURCHASE_INTENT</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>['OTHER']</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>['PRICE_VALUE']</t>
+        </is>
+      </c>
+      <c r="H53" t="b">
+        <v>0</v>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>['NONE']</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>['NONE']</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>['LOWER_PRICE']</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M53" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>I saved this after a friend suggested it</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>PRICE_VALUE</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>MASCARA_PRICE_VALUE</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>PRICE_VALUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>NEW043</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Synthetic Test</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>The shade is almost perfect; I am waiting because the tube size looks small for the price.</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Lip Gloss</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>WAITING_FOR_BETTER_VALUE</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>['SIZE_FORMAT']</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>['PRICE_VALUE']</t>
+        </is>
+      </c>
+      <c r="H54" t="b">
+        <v>0</v>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>['NONE']</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>['NONE']</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>['LOWER_PRICE']</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M54" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>The shade is almost perfect</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>PRICE_VALUE</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>LIP_GLOSS_PRICE_VALUE</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>PRICE_VALUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>NEW044</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Synthetic Test</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>I am deciding between a brightening serum and a barrier-focused one, and this product sits in the middle.</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Serum</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>GENUINE_PURCHASE_INTENT</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>['SUITABILITY']</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>['SUITABILITY']</t>
+        </is>
+      </c>
+      <c r="H55" t="b">
+        <v>0</v>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>['NONE']</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>['NONE']</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>['SUITABILITY_CONFIDENCE']</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M55" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>I am deciding between a brightening serum and a barrier-focused one</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>SUITABILITY</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>SERUM_SUITABILITY</t>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>SUITABILITY</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>NEW045</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Synthetic Test</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>I need a sunscreen that feels comfortable enough for daily use, so I am comparing textures rather than protection claims alone.</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Sunscreen</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>COMPARISON</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>['COMPARISON']</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>['COMPARISON']</t>
+        </is>
+      </c>
+      <c r="H56" t="b">
+        <v>1</v>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>['SIMILAR_PRODUCT']</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>['NONE']</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>['BETTER_ALTERNATIVE']</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M56" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>I need a sunscreen that feels comfortable enough for daily use</t>
+        </is>
+      </c>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>COMPARISON</t>
+        </is>
+      </c>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>SUNSCREEN_COMPARISON</t>
+        </is>
+      </c>
+      <c r="Q56" t="inlineStr">
+        <is>
+          <t>COMPARISON</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>NEW046</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Synthetic Test</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>The product has the features I want, but I'm not sure it fits into the steps I already use morning and night.</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Skincare</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>GENUINE_PURCHASE_INTENT</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>['OTHER']</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>['PRICE_VALUE']</t>
+        </is>
+      </c>
+      <c r="H57" t="b">
+        <v>0</v>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>['NONE']</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>['NONE']</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>['LOWER_PRICE']</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M57" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>The product has the features I want</t>
+        </is>
+      </c>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>PRICE_VALUE</t>
+        </is>
+      </c>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>SKINCARE_PRICE_VALUE</t>
+        </is>
+      </c>
+      <c r="Q57" t="inlineStr">
+        <is>
+          <t>PRICE_VALUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>NEW047</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Synthetic Test</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>The online swatch looks warmer than the shade description, so I am waiting for more real-life photos.</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Lipstick</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>GENUINE_PURCHASE_INTENT</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>['SHADE']</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>['SHADE_CONFIDENCE']</t>
+        </is>
+      </c>
+      <c r="H58" t="b">
+        <v>0</v>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>['NONE']</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>['NONE']</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>['SHADE_CONFIRMATION']</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M58" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>The online swatch looks warmer than the shade description</t>
+        </is>
+      </c>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t>SHADE_CONFIDENCE</t>
+        </is>
+      </c>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>LIPSTICK_SHADE_CONFIDENCE</t>
+        </is>
+      </c>
+      <c r="Q58" t="inlineStr">
+        <is>
+          <t>SHADE_CONFIDENCE</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>NEW048</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Synthetic Test</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>I am unsure whether my usual shade translates to this brand, even though the formula itself looks ideal.</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Foundation</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>GENUINE_PURCHASE_INTENT</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>['SHADE']</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>['SHADE_CONFIDENCE']</t>
+        </is>
+      </c>
+      <c r="H59" t="b">
+        <v>0</v>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>['NONE']</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>['NONE']</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>['SHADE_CONFIRMATION']</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M59" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>I am unsure whether my usual shade translates to this brand</t>
+        </is>
+      </c>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>SHADE_CONFIDENCE</t>
+        </is>
+      </c>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>FOUNDATION_SHADE_CONFIDENCE</t>
+        </is>
+      </c>
+      <c r="Q59" t="inlineStr">
+        <is>
+          <t>SHADE_CONFIDENCE</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>NEW049</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Synthetic Test</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>I keep checking the shade wheel because two options look nearly identical on screen.</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Concealer</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>GENUINE_PURCHASE_INTENT</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>['SHADE']</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>['SHADE_CONFIDENCE']</t>
+        </is>
+      </c>
+      <c r="H60" t="b">
+        <v>0</v>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>['NONE']</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>['NONE']</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>['SHADE_CONFIRMATION']</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M60" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>I keep checking the shade wheel because two options look nearly identical on screen</t>
+        </is>
+      </c>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>SHADE_CONFIDENCE</t>
+        </is>
+      </c>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>CONCEALER_SHADE_CONFIDENCE</t>
+        </is>
+      </c>
+      <c r="Q60" t="inlineStr">
+        <is>
+          <t>SHADE_CONFIDENCE</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>NEW050</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Synthetic Test</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>I like the colour, but I am trying to decide whether cream or powder makes more sense for my routine.</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Blush</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>GENUINE_PURCHASE_INTENT</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>['SHADE']</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>['SHADE_CONFIDENCE']</t>
+        </is>
+      </c>
+      <c r="H61" t="b">
+        <v>0</v>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>['NONE']</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>['NONE']</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>['SHADE_CONFIRMATION']</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M61" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>I like the colour</t>
+        </is>
+      </c>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t>SHADE_CONFIDENCE</t>
+        </is>
+      </c>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>BLUSH_SHADE_CONFIDENCE</t>
+        </is>
+      </c>
+      <c r="Q61" t="inlineStr">
+        <is>
+          <t>SHADE_CONFIDENCE</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>NEW051</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Synthetic Test</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>I want lift without a crunchy finish, so I am reading through comments before committing.</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Mascara</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>GENUINE_PURCHASE_INTENT</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>['OTHER']</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>['PRICE_VALUE']</t>
+        </is>
+      </c>
+      <c r="H62" t="b">
+        <v>0</v>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>['NONE']</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>['NONE']</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>['LOWER_PRICE']</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M62" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>I want lift without a crunchy finish</t>
+        </is>
+      </c>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t>PRICE_VALUE</t>
+        </is>
+      </c>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>MASCARA_PRICE_VALUE</t>
+        </is>
+      </c>
+      <c r="Q62" t="inlineStr">
+        <is>
+          <t>PRICE_VALUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>NEW052</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Synthetic Test</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>I am torn between this transparent gloss and a tinted one because I don't know which I will use more often.</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Lip Gloss</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>GENUINE_PURCHASE_INTENT</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>['OTHER']</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>['PRICE_VALUE']</t>
+        </is>
+      </c>
+      <c r="H63" t="b">
+        <v>0</v>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>['NONE']</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>['NONE']</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>['LOWER_PRICE']</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M63" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>I am torn between this transparent gloss and a tinted one because I don't know which I will use more often</t>
+        </is>
+      </c>
+      <c r="O63" t="inlineStr">
+        <is>
+          <t>PRICE_VALUE</t>
+        </is>
+      </c>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>LIP_GLOSS_PRICE_VALUE</t>
+        </is>
+      </c>
+      <c r="Q63" t="inlineStr">
+        <is>
+          <t>PRICE_VALUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>NEW053</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Synthetic Test</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>This one is still saved because I want to compare how quickly people noticed results with other products for the same concern.</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Serum</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>COMPARISON</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>['COMPARISON']</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>['COMPARISON']</t>
+        </is>
+      </c>
+      <c r="H64" t="b">
+        <v>1</v>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>['SIMILAR_PRODUCT']</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>['NONE']</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>['BETTER_ALTERNATIVE']</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M64" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>This one is still saved because I want to compare how quickly people noticed results with other products for the same concern</t>
+        </is>
+      </c>
+      <c r="O64" t="inlineStr">
+        <is>
+          <t>COMPARISON</t>
+        </is>
+      </c>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>SERUM_COMPARISON</t>
+        </is>
+      </c>
+      <c r="Q64" t="inlineStr">
+        <is>
+          <t>COMPARISON</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>NEW054</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Synthetic Test</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>The product sounds good, but I am concerned it may feel heavy when I reapply over makeup.</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Sunscreen</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>GENUINE_PURCHASE_INTENT</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>['OTHER']</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>['PRICE_VALUE']</t>
+        </is>
+      </c>
+      <c r="H65" t="b">
+        <v>0</v>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>['NONE']</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>['NONE']</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>['LOWER_PRICE']</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M65" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>The product sounds good</t>
+        </is>
+      </c>
+      <c r="O65" t="inlineStr">
+        <is>
+          <t>PRICE_VALUE</t>
+        </is>
+      </c>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>SUNSCREEN_PRICE_VALUE</t>
+        </is>
+      </c>
+      <c r="Q65" t="inlineStr">
+        <is>
+          <t>PRICE_VALUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>NEW055</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Synthetic Test</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>I want something gentle enough for daily use, so irritation reports matter more to me than the star rating.</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Skincare</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>GENUINE_PURCHASE_INTENT</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>['SUITABILITY']</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>['SUITABILITY']</t>
+        </is>
+      </c>
+      <c r="H66" t="b">
+        <v>0</v>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>['NONE']</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>['NONE']</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>['SUITABILITY_CONFIDENCE']</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M66" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>I want something gentle enough for daily use</t>
+        </is>
+      </c>
+      <c r="O66" t="inlineStr">
+        <is>
+          <t>SUITABILITY</t>
+        </is>
+      </c>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>SKINCARE_SUITABILITY</t>
+        </is>
+      </c>
+      <c r="Q66" t="inlineStr">
+        <is>
+          <t>SUITABILITY</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>NEW056</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Synthetic Test</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>The colour is within my usual range, but I haven't seen enough photos in indoor lighting to feel confident.</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Lipstick</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>GENUINE_PURCHASE_INTENT</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>['SHADE']</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>['SHADE_CONFIDENCE']</t>
+        </is>
+      </c>
+      <c r="H67" t="b">
+        <v>0</v>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>['NONE']</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>['NONE']</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>['SHADE_CONFIRMATION']</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M67" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>The colour is within my usual range</t>
+        </is>
+      </c>
+      <c r="O67" t="inlineStr">
+        <is>
+          <t>SHADE_CONFIDENCE</t>
+        </is>
+      </c>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>LIPSTICK_SHADE_CONFIDENCE</t>
+        </is>
+      </c>
+      <c r="Q67" t="inlineStr">
+        <is>
+          <t>SHADE_CONFIDENCE</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>NEW057</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Synthetic Test</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>I like the brand reputation, but another brand offers the same coverage with a more skin-like finish.</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Foundation</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>WAITING_FOR_BETTER_VALUE</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>['PRICE_VALUE']</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>['PRICE_VALUE']</t>
+        </is>
+      </c>
+      <c r="H68" t="b">
+        <v>0</v>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>['NONE']</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>['NONE']</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>['LOWER_PRICE']</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M68" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>but another brand offers the same coverage with a more skin-like finish</t>
+        </is>
+      </c>
+      <c r="O68" t="inlineStr">
+        <is>
+          <t>PRICE_VALUE</t>
+        </is>
+      </c>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>FOUNDATION_PRICE_VALUE</t>
+        </is>
+      </c>
+      <c r="Q68" t="inlineStr">
+        <is>
+          <t>PRICE_VALUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>NEW058</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Synthetic Test</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>I need to know if the formula is flexible enough for both spot concealing and under-eye use.</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Concealer</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>GENUINE_PURCHASE_INTENT</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>['OTHER']</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>['PRICE_VALUE']</t>
+        </is>
+      </c>
+      <c r="H69" t="b">
+        <v>0</v>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>['NONE']</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>['NONE']</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>['LOWER_PRICE']</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M69" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>I need to know if the formula is flexible enough for both spot concealing and under-eye use</t>
+        </is>
+      </c>
+      <c r="O69" t="inlineStr">
+        <is>
+          <t>PRICE_VALUE</t>
+        </is>
+      </c>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>CONCEALER_PRICE_VALUE</t>
+        </is>
+      </c>
+      <c r="Q69" t="inlineStr">
+        <is>
+          <t>PRICE_VALUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>NEW059</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Synthetic Test</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>The shade seems flattering, but I'm looking for a finish that won't emphasize texture on my cheeks.</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Blush</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>GENUINE_PURCHASE_INTENT</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>['SHADE']</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>['SHADE_CONFIDENCE']</t>
+        </is>
+      </c>
+      <c r="H70" t="b">
+        <v>0</v>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>['NONE']</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>['NONE']</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>['SHADE_CONFIRMATION']</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M70" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>The shade seems flattering</t>
+        </is>
+      </c>
+      <c r="O70" t="inlineStr">
+        <is>
+          <t>SHADE_CONFIDENCE</t>
+        </is>
+      </c>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>BLUSH_SHADE_CONFIDENCE</t>
+        </is>
+      </c>
+      <c r="Q70" t="inlineStr">
+        <is>
+          <t>SHADE_CONFIDENCE</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>NEW060</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Synthetic Test</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>I care about easy removal because I wear mascara every day, so waterproofing is actually a downside for me.</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Mascara</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>GENUINE_PURCHASE_INTENT</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>['PERFORMANCE_DOUBT']</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>['PRODUCT_QUALITY']</t>
+        </is>
+      </c>
+      <c r="H71" t="b">
+        <v>0</v>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>['NONE']</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>['NONE']</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>['PRODUCT_DEMO']</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M71" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t>I care about easy removal because I wear mascara every day</t>
+        </is>
+      </c>
+      <c r="O71" t="inlineStr">
+        <is>
+          <t>QUALITY_TRUST</t>
+        </is>
+      </c>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>MASCARA_QUALITY_TRUST</t>
+        </is>
+      </c>
+      <c r="Q71" t="inlineStr">
+        <is>
+          <t>QUALITY_TRUST</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>NEW061</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Synthetic Test</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>I saved it for the texture, then started questioning whether the applicator will make precise application difficult.</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>Lip Gloss</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>GENUINE_PURCHASE_INTENT</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>['OTHER']</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>['PRICE_VALUE']</t>
+        </is>
+      </c>
+      <c r="H72" t="b">
+        <v>0</v>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>['NONE']</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>['NONE']</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>['LOWER_PRICE']</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M72" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t>I saved it for the texture</t>
+        </is>
+      </c>
+      <c r="O72" t="inlineStr">
+        <is>
+          <t>PRICE_VALUE</t>
+        </is>
+      </c>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>LIP_GLOSS_PRICE_VALUE</t>
+        </is>
+      </c>
+      <c r="Q72" t="inlineStr">
+        <is>
+          <t>PRICE_VALUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>NEW062</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Synthetic Test</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>I'm hesitant because I already have a serum with a similar purpose and don't want overlapping products.</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>Serum</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>GENUINE_PURCHASE_INTENT</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>['OTHER']</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>['PRICE_VALUE']</t>
+        </is>
+      </c>
+      <c r="H73" t="b">
+        <v>0</v>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>['NONE']</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>['NONE']</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>['LOWER_PRICE']</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M73" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>I'm hesitant because I already have a serum with a similar purpose and don't want overlapping products</t>
+        </is>
+      </c>
+      <c r="O73" t="inlineStr">
+        <is>
+          <t>PRICE_VALUE</t>
+        </is>
+      </c>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>SERUM_PRICE_VALUE</t>
+        </is>
+      </c>
+      <c r="Q73" t="inlineStr">
+        <is>
+          <t>PRICE_VALUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>NEW063</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Synthetic Test</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>I am comparing how this sits under concealer with two other sunscreens before I settle on one.</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>Sunscreen</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>COMPARISON</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>['COMPARISON']</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>['COMPARISON']</t>
+        </is>
+      </c>
+      <c r="H74" t="b">
+        <v>1</v>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>['SIMILAR_PRODUCT']</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>['NONE']</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>['BETTER_ALTERNATIVE']</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M74" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="N74" t="inlineStr">
+        <is>
+          <t>I am comparing how this sits under concealer with two other sunscreens before I settle on one</t>
+        </is>
+      </c>
+      <c r="O74" t="inlineStr">
+        <is>
+          <t>COMPARISON</t>
+        </is>
+      </c>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>SUNSCREEN_COMPARISON</t>
+        </is>
+      </c>
+      <c r="Q74" t="inlineStr">
+        <is>
+          <t>COMPARISON</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>NEW064</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Synthetic Test</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>I like the packaging and ingredient list, but I am more interested in whether people noticed a real difference after a month.</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>Skincare</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>GENUINE_PURCHASE_INTENT</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>['OTHER']</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>['PRICE_VALUE']</t>
+        </is>
+      </c>
+      <c r="H75" t="b">
+        <v>0</v>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>['NONE']</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>['NONE']</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>['LOWER_PRICE']</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M75" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="N75" t="inlineStr">
+        <is>
+          <t>I like the packaging and ingredient list</t>
+        </is>
+      </c>
+      <c r="O75" t="inlineStr">
+        <is>
+          <t>PRICE_VALUE</t>
+        </is>
+      </c>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>SKINCARE_PRICE_VALUE</t>
+        </is>
+      </c>
+      <c r="Q75" t="inlineStr">
+        <is>
+          <t>PRICE_VALUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>NEW065</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Synthetic Test</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>The finish is what attracts me, but I would change the shade if there is a more flattering neutral in the same range.</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>Lipstick</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>GENUINE_PURCHASE_INTENT</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>['SHADE']</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>['SHADE_CONFIDENCE']</t>
+        </is>
+      </c>
+      <c r="H76" t="b">
+        <v>0</v>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>['NONE']</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>['NONE']</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>['SHADE_CONFIRMATION']</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M76" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="N76" t="inlineStr">
+        <is>
+          <t>The finish is what attracts me</t>
+        </is>
+      </c>
+      <c r="O76" t="inlineStr">
+        <is>
+          <t>SHADE_CONFIDENCE</t>
+        </is>
+      </c>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>LIPSTICK_SHADE_CONFIDENCE</t>
+        </is>
+      </c>
+      <c r="Q76" t="inlineStr">
+        <is>
+          <t>SHADE_CONFIDENCE</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>NEW066</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Synthetic Test</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>I usually buy medium coverage, and I'm checking whether this can be layered without becoming cakey.</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>Foundation</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>GENUINE_PURCHASE_INTENT</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>['FINISH']</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>['PRODUCT_QUALITY']</t>
+        </is>
+      </c>
+      <c r="H77" t="b">
+        <v>0</v>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>['NONE']</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>['NONE']</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>['PRODUCT_DEMO']</t>
+        </is>
+      </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M77" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="N77" t="inlineStr">
+        <is>
+          <t>I usually buy medium coverage</t>
+        </is>
+      </c>
+      <c r="O77" t="inlineStr">
+        <is>
+          <t>QUALITY_TRUST</t>
+        </is>
+      </c>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>FOUNDATION_QUALITY_TRUST</t>
+        </is>
+      </c>
+      <c r="Q77" t="inlineStr">
+        <is>
+          <t>QUALITY_TRUST</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>NEW067</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Synthetic Test</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>The product seems versatile, but I want to know if the finish stays natural after setting powder.</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>Concealer</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>GENUINE_PURCHASE_INTENT</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>['OTHER']</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>['PRICE_VALUE']</t>
+        </is>
+      </c>
+      <c r="H78" t="b">
+        <v>0</v>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>['NONE']</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>['NONE']</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>['LOWER_PRICE']</t>
+        </is>
+      </c>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M78" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="N78" t="inlineStr">
+        <is>
+          <t>but I want to know if the finish stays natural after setting powder</t>
+        </is>
+      </c>
+      <c r="O78" t="inlineStr">
+        <is>
+          <t>PRICE_VALUE</t>
+        </is>
+      </c>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>CONCEALER_PRICE_VALUE</t>
+        </is>
+      </c>
+      <c r="Q78" t="inlineStr">
+        <is>
+          <t>PRICE_VALUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>NEW068</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Synthetic Test</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>I am considering this because it looks easy to build up, which matters more to me than a very strong pigment.</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>Blush</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>WAITING_FOR_BETTER_VALUE</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>['PRICE_VALUE']</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>['PRICE_VALUE']</t>
+        </is>
+      </c>
+      <c r="H79" t="b">
+        <v>0</v>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>['NONE']</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>['NONE']</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>['LOWER_PRICE']</t>
+        </is>
+      </c>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M79" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="N79" t="inlineStr">
+        <is>
+          <t>I am considering this because it looks easy to build up</t>
+        </is>
+      </c>
+      <c r="O79" t="inlineStr">
+        <is>
+          <t>PRICE_VALUE</t>
+        </is>
+      </c>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>BLUSH_PRICE_VALUE</t>
+        </is>
+      </c>
+      <c r="Q79" t="inlineStr">
+        <is>
+          <t>PRICE_VALUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>NEW069</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Synthetic Test</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>I want a formula that holds a curl, and I'm comparing before-and-after photos rather than just star ratings.</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>Mascara</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>COMPARISON</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>['COMPARISON']</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>['COMPARISON']</t>
+        </is>
+      </c>
+      <c r="H80" t="b">
+        <v>1</v>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>['SIMILAR_PRODUCT']</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>['NONE']</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>['BETTER_ALTERNATIVE']</t>
+        </is>
+      </c>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M80" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="N80" t="inlineStr">
+        <is>
+          <t>I want a formula that holds a curl</t>
+        </is>
+      </c>
+      <c r="O80" t="inlineStr">
+        <is>
+          <t>COMPARISON</t>
+        </is>
+      </c>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>MASCARA_COMPARISON</t>
+        </is>
+      </c>
+      <c r="Q80" t="inlineStr">
+        <is>
+          <t>COMPARISON</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>NEW070</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Synthetic Test</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>The brand is familiar, but I haven't decided because I already own a similar gloss from the same line.</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>Lip Gloss</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>BOOKMARK</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>['NO_NEED']</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>['OTHER']</t>
+        </is>
+      </c>
+      <c r="H81" t="b">
+        <v>0</v>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>['NONE']</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>['NONE']</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>['BETTER_REVIEWS']</t>
+        </is>
+      </c>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M81" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="N81" t="inlineStr">
+        <is>
+          <t>The brand is familiar</t>
+        </is>
+      </c>
+      <c r="O81" t="inlineStr">
+        <is>
+          <t>INTENT_DECAY</t>
+        </is>
+      </c>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>LIP_GLOSS_INTENT_DECAY</t>
+        </is>
+      </c>
+      <c r="Q81" t="inlineStr">
+        <is>
+          <t>INTENT_DECAY</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>NEW071</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Synthetic Test</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>I am waiting to see whether this works with my existing moisturizer without pilling.</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>Serum</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>GENUINE_PURCHASE_INTENT</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>['OTHER']</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>['PRICE_VALUE']</t>
+        </is>
+      </c>
+      <c r="H82" t="b">
+        <v>0</v>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>['NONE']</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>['NONE']</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>['LOWER_PRICE']</t>
+        </is>
+      </c>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M82" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="N82" t="inlineStr">
+        <is>
+          <t>I am waiting to see whether this works with my existing moisturizer without pilling</t>
+        </is>
+      </c>
+      <c r="O82" t="inlineStr">
+        <is>
+          <t>PRICE_VALUE</t>
+        </is>
+      </c>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>SERUM_PRICE_VALUE</t>
+        </is>
+      </c>
+      <c r="Q82" t="inlineStr">
+        <is>
+          <t>PRICE_VALUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>NEW072</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Synthetic Test</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>The product is interesting, but I need a finish that doesn't make my skin look overly shiny by midday.</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>Sunscreen</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>GENUINE_PURCHASE_INTENT</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>['OTHER']</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>['PRICE_VALUE']</t>
+        </is>
+      </c>
+      <c r="H83" t="b">
+        <v>0</v>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>['NONE']</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>['NONE']</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>['LOWER_PRICE']</t>
+        </is>
+      </c>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M83" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="N83" t="inlineStr">
+        <is>
+          <t>but I need a finish that doesn't make my skin look overly shiny by midday</t>
+        </is>
+      </c>
+      <c r="O83" t="inlineStr">
+        <is>
+          <t>PRICE_VALUE</t>
+        </is>
+      </c>
+      <c r="P83" t="inlineStr">
+        <is>
+          <t>SUNSCREEN_PRICE_VALUE</t>
+        </is>
+      </c>
+      <c r="Q83" t="inlineStr">
+        <is>
+          <t>PRICE_VALUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>NEW073</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Synthetic Test</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>I saved this because it targets redness, but I am checking whether the texture will work under makeup.</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>Skincare</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>GENUINE_PURCHASE_INTENT</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>['OTHER']</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>['PRICE_VALUE']</t>
+        </is>
+      </c>
+      <c r="H84" t="b">
+        <v>0</v>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>['NONE']</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>['NONE']</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>['LOWER_PRICE']</t>
+        </is>
+      </c>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M84" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="N84" t="inlineStr">
+        <is>
+          <t>I saved this because it targets redness</t>
+        </is>
+      </c>
+      <c r="O84" t="inlineStr">
+        <is>
+          <t>PRICE_VALUE</t>
+        </is>
+      </c>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t>SKINCARE_PRICE_VALUE</t>
+        </is>
+      </c>
+      <c r="Q84" t="inlineStr">
+        <is>
+          <t>PRICE_VALUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>NEW074</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Synthetic Test</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>I would consider a different shade if the undertone matched better, even though I prefer the original colour name.</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>Lipstick</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>GENUINE_PURCHASE_INTENT</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>['SHADE']</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>['SHADE_CONFIDENCE']</t>
+        </is>
+      </c>
+      <c r="H85" t="b">
+        <v>0</v>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>['NONE']</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>['NONE']</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>['SHADE_CONFIRMATION']</t>
+        </is>
+      </c>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M85" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="N85" t="inlineStr">
+        <is>
+          <t>I would consider a different shade if the undertone matched better</t>
+        </is>
+      </c>
+      <c r="O85" t="inlineStr">
+        <is>
+          <t>SHADE_CONFIDENCE</t>
+        </is>
+      </c>
+      <c r="P85" t="inlineStr">
+        <is>
+          <t>LIPSTICK_SHADE_CONFIDENCE</t>
+        </is>
+      </c>
+      <c r="Q85" t="inlineStr">
+        <is>
+          <t>SHADE_CONFIDENCE</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>NEW075</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Synthetic Test</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>This looks like a good everyday option, but I am not sure I want to replace my current foundation yet.</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>Foundation</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>GENUINE_PURCHASE_INTENT</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>['OTHER']</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>['PRICE_VALUE']</t>
+        </is>
+      </c>
+      <c r="H86" t="b">
+        <v>0</v>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>['NONE']</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>['NONE']</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>['LOWER_PRICE']</t>
+        </is>
+      </c>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M86" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="N86" t="inlineStr">
+        <is>
+          <t>This looks like a good everyday option</t>
+        </is>
+      </c>
+      <c r="O86" t="inlineStr">
+        <is>
+          <t>PRICE_VALUE</t>
+        </is>
+      </c>
+      <c r="P86" t="inlineStr">
+        <is>
+          <t>FOUNDATION_PRICE_VALUE</t>
+        </is>
+      </c>
+      <c r="Q86" t="inlineStr">
+        <is>
+          <t>PRICE_VALUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>NEW076</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Synthetic Test</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>I am looking for a close skin match rather than a brightening shade, so the available tones are making me hesitate.</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>Concealer</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>GENUINE_PURCHASE_INTENT</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>['SHADE']</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>['SHADE_CONFIDENCE']</t>
+        </is>
+      </c>
+      <c r="H87" t="b">
+        <v>0</v>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>['NONE']</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>['NONE']</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>['SHADE_CONFIRMATION']</t>
+        </is>
+      </c>
+      <c r="L87" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M87" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="N87" t="inlineStr">
+        <is>
+          <t>I am looking for a close skin match rather than a brightening shade</t>
+        </is>
+      </c>
+      <c r="O87" t="inlineStr">
+        <is>
+          <t>SHADE_CONFIDENCE</t>
+        </is>
+      </c>
+      <c r="P87" t="inlineStr">
+        <is>
+          <t>CONCEALER_SHADE_CONFIDENCE</t>
+        </is>
+      </c>
+      <c r="Q87" t="inlineStr">
+        <is>
+          <t>SHADE_CONFIDENCE</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>NEW077</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Synthetic Test</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>The colour is appealing, but I want to know if it fades evenly or disappears in patches.</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>Blush</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>GENUINE_PURCHASE_INTENT</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>['PERFORMANCE_DOUBT']</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>['PRODUCT_QUALITY']</t>
+        </is>
+      </c>
+      <c r="H88" t="b">
+        <v>0</v>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>['NONE']</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>['NONE']</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>['PRODUCT_DEMO']</t>
+        </is>
+      </c>
+      <c r="L88" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M88" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="N88" t="inlineStr">
+        <is>
+          <t>The colour is appealing</t>
+        </is>
+      </c>
+      <c r="O88" t="inlineStr">
+        <is>
+          <t>QUALITY_TRUST</t>
+        </is>
+      </c>
+      <c r="P88" t="inlineStr">
+        <is>
+          <t>BLUSH_QUALITY_TRUST</t>
+        </is>
+      </c>
+      <c r="Q88" t="inlineStr">
+        <is>
+          <t>QUALITY_TRUST</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>NEW078</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Synthetic Test</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>I like the promise of separation, but I'm checking if it also adds enough drama for evenings.</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>Mascara</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>GENUINE_PURCHASE_INTENT</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>['PERFORMANCE_DOUBT']</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>['PRODUCT_QUALITY']</t>
+        </is>
+      </c>
+      <c r="H89" t="b">
+        <v>0</v>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>['NONE']</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>['NONE']</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>['PRODUCT_DEMO']</t>
+        </is>
+      </c>
+      <c r="L89" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M89" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="N89" t="inlineStr">
+        <is>
+          <t>I like the promise of separation</t>
+        </is>
+      </c>
+      <c r="O89" t="inlineStr">
+        <is>
+          <t>QUALITY_TRUST</t>
+        </is>
+      </c>
+      <c r="P89" t="inlineStr">
+        <is>
+          <t>MASCARA_QUALITY_TRUST</t>
+        </is>
+      </c>
+      <c r="Q89" t="inlineStr">
+        <is>
+          <t>QUALITY_TRUST</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>NEW079</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Synthetic Test</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>I am mostly deciding between comfort and shine; the more glossy formulas tend to feel tackier to me.</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>Lip Gloss</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>GENUINE_PURCHASE_INTENT</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>['OTHER']</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>['PRICE_VALUE']</t>
+        </is>
+      </c>
+      <c r="H90" t="b">
+        <v>0</v>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>['NONE']</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>['NONE']</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>['LOWER_PRICE']</t>
+        </is>
+      </c>
+      <c r="L90" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M90" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="N90" t="inlineStr">
+        <is>
+          <t>I am mostly deciding between comfort and shine</t>
+        </is>
+      </c>
+      <c r="O90" t="inlineStr">
+        <is>
+          <t>PRICE_VALUE</t>
+        </is>
+      </c>
+      <c r="P90" t="inlineStr">
+        <is>
+          <t>LIP_GLOSS_PRICE_VALUE</t>
+        </is>
+      </c>
+      <c r="Q90" t="inlineStr">
+        <is>
+          <t>PRICE_VALUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>NEW080</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Synthetic Test</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>The product is saved for later because I want to finish the one I have before introducing another active.</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>Serum</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>GENUINE_PURCHASE_INTENT</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>['OTHER']</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>['PRICE_VALUE']</t>
+        </is>
+      </c>
+      <c r="H91" t="b">
+        <v>0</v>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>['NONE']</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>['NONE']</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>['LOWER_PRICE']</t>
+        </is>
+      </c>
+      <c r="L91" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M91" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="N91" t="inlineStr">
+        <is>
+          <t>The product is saved for later because I want to finish the one I have before introducing another active</t>
+        </is>
+      </c>
+      <c r="O91" t="inlineStr">
+        <is>
+          <t>PRICE_VALUE</t>
+        </is>
+      </c>
+      <c r="P91" t="inlineStr">
+        <is>
+          <t>SERUM_PRICE_VALUE</t>
+        </is>
+      </c>
+      <c r="Q91" t="inlineStr">
+        <is>
+          <t>PRICE_VALUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>NEW081</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Synthetic Test</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>I am comparing this with a stick sunscreen for touch-ups because convenience matters when I am out all day.</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>Sunscreen</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>COMPARISON</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>['COMPARISON']</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>['COMPARISON']</t>
+        </is>
+      </c>
+      <c r="H92" t="b">
+        <v>1</v>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>['SIMILAR_PRODUCT']</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>['NONE']</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>['BETTER_ALTERNATIVE']</t>
+        </is>
+      </c>
+      <c r="L92" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M92" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="N92" t="inlineStr">
+        <is>
+          <t>I am comparing this with a stick sunscreen for touch-ups because convenience matters when I am out all day</t>
+        </is>
+      </c>
+      <c r="O92" t="inlineStr">
+        <is>
+          <t>COMPARISON</t>
+        </is>
+      </c>
+      <c r="P92" t="inlineStr">
+        <is>
+          <t>SUNSCREEN_COMPARISON</t>
+        </is>
+      </c>
+      <c r="Q92" t="inlineStr">
+        <is>
+          <t>COMPARISON</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>NEW082</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Synthetic Test</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>The reviews mention different experiences, so I am trying to figure out whether skin type explains the difference.</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>Skincare</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>GENUINE_PURCHASE_INTENT</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>['SUITABILITY']</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>['SUITABILITY']</t>
+        </is>
+      </c>
+      <c r="H93" t="b">
+        <v>0</v>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>['NONE']</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>['NONE']</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>['SUITABILITY_CONFIDENCE']</t>
+        </is>
+      </c>
+      <c r="L93" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M93" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="N93" t="inlineStr">
+        <is>
+          <t>so I am trying to figure out whether skin type explains the difference</t>
+        </is>
+      </c>
+      <c r="O93" t="inlineStr">
+        <is>
+          <t>SUITABILITY</t>
+        </is>
+      </c>
+      <c r="P93" t="inlineStr">
+        <is>
+          <t>SKINCARE_SUITABILITY</t>
+        </is>
+      </c>
+      <c r="Q93" t="inlineStr">
+        <is>
+          <t>SUITABILITY</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>NEW083</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Synthetic Test</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>I like everything except the finish; I want the same shade family in a cream formula.</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>Lipstick</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>GENUINE_PURCHASE_INTENT</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>['SHADE']</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>['SHADE_CONFIDENCE']</t>
+        </is>
+      </c>
+      <c r="H94" t="b">
+        <v>0</v>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>['NONE']</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>['NONE']</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>['SHADE_CONFIRMATION']</t>
+        </is>
+      </c>
+      <c r="L94" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M94" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="N94" t="inlineStr">
+        <is>
+          <t>I like everything except the finish</t>
+        </is>
+      </c>
+      <c r="O94" t="inlineStr">
+        <is>
+          <t>SHADE_CONFIDENCE</t>
+        </is>
+      </c>
+      <c r="P94" t="inlineStr">
+        <is>
+          <t>LIPSTICK_SHADE_CONFIDENCE</t>
+        </is>
+      </c>
+      <c r="Q94" t="inlineStr">
+        <is>
+          <t>SHADE_CONFIDENCE</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>NEW084</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Synthetic Test</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>I am considering this because I heard it works well in humid weather, but I want evidence beyond influencer videos.</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>Foundation</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>GENUINE_PURCHASE_INTENT</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>['OTHER']</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>['PRICE_VALUE']</t>
+        </is>
+      </c>
+      <c r="H95" t="b">
+        <v>0</v>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>['NONE']</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>['NONE']</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>['LOWER_PRICE']</t>
+        </is>
+      </c>
+      <c r="L95" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M95" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="N95" t="inlineStr">
+        <is>
+          <t>I am considering this because I heard it works well in humid weather</t>
+        </is>
+      </c>
+      <c r="O95" t="inlineStr">
+        <is>
+          <t>PRICE_VALUE</t>
+        </is>
+      </c>
+      <c r="P95" t="inlineStr">
+        <is>
+          <t>FOUNDATION_PRICE_VALUE</t>
+        </is>
+      </c>
+      <c r="Q95" t="inlineStr">
+        <is>
+          <t>PRICE_VALUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>NEW085</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Synthetic Test</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>The shade selection looks good, yet I need to know if it oxidizes after application.</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>Concealer</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>GENUINE_PURCHASE_INTENT</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>['SHADE']</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>['SHADE_CONFIDENCE']</t>
+        </is>
+      </c>
+      <c r="H96" t="b">
+        <v>0</v>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>['NONE']</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>['NONE']</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>['SHADE_CONFIRMATION']</t>
+        </is>
+      </c>
+      <c r="L96" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M96" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="N96" t="inlineStr">
+        <is>
+          <t>The shade selection looks good</t>
+        </is>
+      </c>
+      <c r="O96" t="inlineStr">
+        <is>
+          <t>SHADE_CONFIDENCE</t>
+        </is>
+      </c>
+      <c r="P96" t="inlineStr">
+        <is>
+          <t>CONCEALER_SHADE_CONFIDENCE</t>
+        </is>
+      </c>
+      <c r="Q96" t="inlineStr">
+        <is>
+          <t>SHADE_CONFIDENCE</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>NEW086</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Synthetic Test</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>I am saving this while I decide between a soft matte look and a dewy finish for everyday makeup.</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>Blush</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>GENUINE_PURCHASE_INTENT</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>['OTHER']</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>['PRICE_VALUE']</t>
+        </is>
+      </c>
+      <c r="H97" t="b">
+        <v>0</v>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>['NONE']</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>['NONE']</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>['LOWER_PRICE']</t>
+        </is>
+      </c>
+      <c r="L97" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M97" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="N97" t="inlineStr">
+        <is>
+          <t>I am saving this while I decide between a soft matte look and a dewy finish for everyday makeup</t>
+        </is>
+      </c>
+      <c r="O97" t="inlineStr">
+        <is>
+          <t>PRICE_VALUE</t>
+        </is>
+      </c>
+      <c r="P97" t="inlineStr">
+        <is>
+          <t>BLUSH_PRICE_VALUE</t>
+        </is>
+      </c>
+      <c r="Q97" t="inlineStr">
+        <is>
+          <t>PRICE_VALUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>NEW087</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Synthetic Test</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>I care about the wand more than the packaging, and I am comparing curved versus straight brushes.</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>Mascara</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>COMPARISON</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>['COMPARISON']</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>['COMPARISON']</t>
+        </is>
+      </c>
+      <c r="H98" t="b">
+        <v>1</v>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>['SIMILAR_PRODUCT']</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>['NONE']</t>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>['BETTER_ALTERNATIVE']</t>
+        </is>
+      </c>
+      <c r="L98" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M98" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="N98" t="inlineStr">
+        <is>
+          <t>I care about the wand more than the packaging</t>
+        </is>
+      </c>
+      <c r="O98" t="inlineStr">
+        <is>
+          <t>COMPARISON</t>
+        </is>
+      </c>
+      <c r="P98" t="inlineStr">
+        <is>
+          <t>MASCARA_COMPARISON</t>
+        </is>
+      </c>
+      <c r="Q98" t="inlineStr">
+        <is>
+          <t>COMPARISON</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>NEW088</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Synthetic Test</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>I want a subtle tint for daily wear, so the brighter shades are making me hesitate.</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>Lip Gloss</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>GENUINE_PURCHASE_INTENT</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>['SHADE']</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>['SHADE_CONFIDENCE']</t>
+        </is>
+      </c>
+      <c r="H99" t="b">
+        <v>0</v>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>['NONE']</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>['NONE']</t>
+        </is>
+      </c>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>['SHADE_CONFIRMATION']</t>
+        </is>
+      </c>
+      <c r="L99" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M99" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="N99" t="inlineStr">
+        <is>
+          <t>so the brighter shades are making me hesitate</t>
+        </is>
+      </c>
+      <c r="O99" t="inlineStr">
+        <is>
+          <t>SHADE_CONFIDENCE</t>
+        </is>
+      </c>
+      <c r="P99" t="inlineStr">
+        <is>
+          <t>LIP_GLOSS_SHADE_CONFIDENCE</t>
+        </is>
+      </c>
+      <c r="Q99" t="inlineStr">
+        <is>
+          <t>SHADE_CONFIDENCE</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>NEW089</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Synthetic Test</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>I am checking whether the texture absorbs quickly enough for use before sunscreen.</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>Serum</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>GENUINE_PURCHASE_INTENT</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>['OTHER']</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>['PRICE_VALUE']</t>
+        </is>
+      </c>
+      <c r="H100" t="b">
+        <v>0</v>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>['NONE']</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>['NONE']</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>['LOWER_PRICE']</t>
+        </is>
+      </c>
+      <c r="L100" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M100" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="N100" t="inlineStr">
+        <is>
+          <t>I am checking whether the texture absorbs quickly enough for use before sunscreen</t>
+        </is>
+      </c>
+      <c r="O100" t="inlineStr">
+        <is>
+          <t>PRICE_VALUE</t>
+        </is>
+      </c>
+      <c r="P100" t="inlineStr">
+        <is>
+          <t>SERUM_PRICE_VALUE</t>
+        </is>
+      </c>
+      <c r="Q100" t="inlineStr">
+        <is>
+          <t>PRICE_VALUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>NEW090</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Synthetic Test</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>The formula seems suitable, but I need something that won't sting my eyes when I sweat.</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>Sunscreen</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>GENUINE_PURCHASE_INTENT</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>['OTHER']</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>['PRICE_VALUE']</t>
+        </is>
+      </c>
+      <c r="H101" t="b">
+        <v>0</v>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>['NONE']</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>['NONE']</t>
+        </is>
+      </c>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>['LOWER_PRICE']</t>
+        </is>
+      </c>
+      <c r="L101" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M101" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="N101" t="inlineStr">
+        <is>
+          <t>The formula seems suitable</t>
+        </is>
+      </c>
+      <c r="O101" t="inlineStr">
+        <is>
+          <t>PRICE_VALUE</t>
+        </is>
+      </c>
+      <c r="P101" t="inlineStr">
+        <is>
+          <t>SUNSCREEN_PRICE_VALUE</t>
+        </is>
+      </c>
+      <c r="Q101" t="inlineStr">
+        <is>
+          <t>PRICE_VALUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>NEW091</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Synthetic Test</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>I am deciding whether this is genuinely different from the products already in my routine.</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>Skincare</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>GENUINE_PURCHASE_INTENT</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>['OTHER']</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>['PRICE_VALUE']</t>
+        </is>
+      </c>
+      <c r="H102" t="b">
+        <v>0</v>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>['NONE']</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>['NONE']</t>
+        </is>
+      </c>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>['LOWER_PRICE']</t>
+        </is>
+      </c>
+      <c r="L102" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M102" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="N102" t="inlineStr">
+        <is>
+          <t>I am deciding whether this is genuinely different from the products already in my routine</t>
+        </is>
+      </c>
+      <c r="O102" t="inlineStr">
+        <is>
+          <t>PRICE_VALUE</t>
+        </is>
+      </c>
+      <c r="P102" t="inlineStr">
+        <is>
+          <t>SKINCARE_PRICE_VALUE</t>
+        </is>
+      </c>
+      <c r="Q102" t="inlineStr">
+        <is>
+          <t>PRICE_VALUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>NEW092</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Synthetic Test</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>This is still on my wishlist because I like the shade, but I want to compare it with two muted alternatives before buying.</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>Lipstick</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>COMPARISON</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>['COMPARISON']</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>['COMPARISON']</t>
+        </is>
+      </c>
+      <c r="H103" t="b">
+        <v>1</v>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>['SIMILAR_PRODUCT']</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>['NONE']</t>
+        </is>
+      </c>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>['BETTER_ALTERNATIVE']</t>
+        </is>
+      </c>
+      <c r="L103" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M103" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="N103" t="inlineStr">
+        <is>
+          <t>This is still on my wishlist because I like the shade</t>
+        </is>
+      </c>
+      <c r="O103" t="inlineStr">
+        <is>
+          <t>COMPARISON</t>
+        </is>
+      </c>
+      <c r="P103" t="inlineStr">
+        <is>
+          <t>LIPSTICK_COMPARISON</t>
+        </is>
+      </c>
+      <c r="Q103" t="inlineStr">
+        <is>
+          <t>COMPARISON</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>NEW093</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Synthetic Test</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>I almost bought it, then realized I am unsure whether the undertone is warm or neutral in person.</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>Foundation</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>GENUINE_PURCHASE_INTENT</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>['SHADE']</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>['SHADE_CONFIDENCE']</t>
+        </is>
+      </c>
+      <c r="H104" t="b">
+        <v>0</v>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>['NONE']</t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>['NONE']</t>
+        </is>
+      </c>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>['SHADE_CONFIRMATION']</t>
+        </is>
+      </c>
+      <c r="L104" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M104" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="N104" t="inlineStr">
+        <is>
+          <t>then realized I am unsure whether the undertone is warm or neutral in person</t>
+        </is>
+      </c>
+      <c r="O104" t="inlineStr">
+        <is>
+          <t>SHADE_CONFIDENCE</t>
+        </is>
+      </c>
+      <c r="P104" t="inlineStr">
+        <is>
+          <t>FOUNDATION_SHADE_CONFIDENCE</t>
+        </is>
+      </c>
+      <c r="Q104" t="inlineStr">
+        <is>
+          <t>SHADE_CONFIDENCE</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>NEW094</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Synthetic Test</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>I saved it after seeing the coverage, but I want to know if it looks natural without a heavy base.</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>Concealer</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>GENUINE_PURCHASE_INTENT</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>['OTHER']</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>['PRICE_VALUE']</t>
+        </is>
+      </c>
+      <c r="H105" t="b">
+        <v>0</v>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>['NONE']</t>
+        </is>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>['NONE']</t>
+        </is>
+      </c>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>['LOWER_PRICE']</t>
+        </is>
+      </c>
+      <c r="L105" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M105" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="N105" t="inlineStr">
+        <is>
+          <t>I saved it after seeing the coverage</t>
+        </is>
+      </c>
+      <c r="O105" t="inlineStr">
+        <is>
+          <t>PRICE_VALUE</t>
+        </is>
+      </c>
+      <c r="P105" t="inlineStr">
+        <is>
+          <t>CONCEALER_PRICE_VALUE</t>
+        </is>
+      </c>
+      <c r="Q105" t="inlineStr">
+        <is>
+          <t>PRICE_VALUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>NEW095</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Synthetic Test</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>The shade looks versatile, and I am mainly waiting for better swatches before deciding.</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>Blush</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>GENUINE_PURCHASE_INTENT</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>['SHADE']</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>['SHADE_CONFIDENCE']</t>
+        </is>
+      </c>
+      <c r="H106" t="b">
+        <v>0</v>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>['NONE']</t>
+        </is>
+      </c>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>['NONE']</t>
+        </is>
+      </c>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>['SHADE_CONFIRMATION']</t>
+        </is>
+      </c>
+      <c r="L106" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M106" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="N106" t="inlineStr">
+        <is>
+          <t>The shade looks versatile</t>
+        </is>
+      </c>
+      <c r="O106" t="inlineStr">
+        <is>
+          <t>SHADE_CONFIDENCE</t>
+        </is>
+      </c>
+      <c r="P106" t="inlineStr">
+        <is>
+          <t>BLUSH_SHADE_CONFIDENCE</t>
+        </is>
+      </c>
+      <c r="Q106" t="inlineStr">
+        <is>
+          <t>SHADE_CONFIDENCE</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>NEW096</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Synthetic Test</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>I am comparing this with a tubing mascara because removing regular formulas annoys me.</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>Mascara</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>COMPARISON</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>['COMPARISON']</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>['COMPARISON']</t>
+        </is>
+      </c>
+      <c r="H107" t="b">
+        <v>1</v>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>['SIMILAR_PRODUCT']</t>
+        </is>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>['NONE']</t>
+        </is>
+      </c>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>['BETTER_ALTERNATIVE']</t>
+        </is>
+      </c>
+      <c r="L107" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M107" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="N107" t="inlineStr">
+        <is>
+          <t>I am comparing this with a tubing mascara because removing regular formulas annoys me</t>
+        </is>
+      </c>
+      <c r="O107" t="inlineStr">
+        <is>
+          <t>COMPARISON</t>
+        </is>
+      </c>
+      <c r="P107" t="inlineStr">
+        <is>
+          <t>MASCARA_COMPARISON</t>
+        </is>
+      </c>
+      <c r="Q107" t="inlineStr">
+        <is>
+          <t>COMPARISON</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>NEW097</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Synthetic Test</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>The finish is attractive, but I am unsure whether the hydration lasts after the gloss fades.</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>Lip Gloss</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>GENUINE_PURCHASE_INTENT</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>['FINISH']</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>['PRODUCT_QUALITY']</t>
+        </is>
+      </c>
+      <c r="H108" t="b">
+        <v>0</v>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>['NONE']</t>
+        </is>
+      </c>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>['NONE']</t>
+        </is>
+      </c>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>['PRODUCT_DEMO']</t>
+        </is>
+      </c>
+      <c r="L108" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M108" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="N108" t="inlineStr">
+        <is>
+          <t>The finish is attractive</t>
+        </is>
+      </c>
+      <c r="O108" t="inlineStr">
+        <is>
+          <t>QUALITY_TRUST</t>
+        </is>
+      </c>
+      <c r="P108" t="inlineStr">
+        <is>
+          <t>LIP_GLOSS_QUALITY_TRUST</t>
+        </is>
+      </c>
+      <c r="Q108" t="inlineStr">
+        <is>
+          <t>QUALITY_TRUST</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>NEW098</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>Synthetic Test</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>I am interested in the product, but I want a clearer idea of what kind of results are realistic.</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>Serum</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>GENUINE_PURCHASE_INTENT</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>['OTHER']</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>['PRICE_VALUE']</t>
+        </is>
+      </c>
+      <c r="H109" t="b">
+        <v>0</v>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>['NONE']</t>
+        </is>
+      </c>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t>['NONE']</t>
+        </is>
+      </c>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>['LOWER_PRICE']</t>
+        </is>
+      </c>
+      <c r="L109" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M109" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="N109" t="inlineStr">
+        <is>
+          <t>I am interested in the product</t>
+        </is>
+      </c>
+      <c r="O109" t="inlineStr">
+        <is>
+          <t>PRICE_VALUE</t>
+        </is>
+      </c>
+      <c r="P109" t="inlineStr">
+        <is>
+          <t>SERUM_PRICE_VALUE</t>
+        </is>
+      </c>
+      <c r="Q109" t="inlineStr">
+        <is>
+          <t>PRICE_VALUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>NEW099</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>Synthetic Test</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>I want something I can wear every day, so fragrance and texture matter more than a small difference in SPF.</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>Sunscreen</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>GENUINE_PURCHASE_INTENT</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>['INGREDIENT_SAFETY']</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>['SUITABILITY']</t>
+        </is>
+      </c>
+      <c r="H110" t="b">
+        <v>0</v>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>['NONE']</t>
+        </is>
+      </c>
+      <c r="J110" t="inlineStr">
+        <is>
+          <t>['NONE']</t>
+        </is>
+      </c>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>['SUITABILITY_CONFIDENCE']</t>
+        </is>
+      </c>
+      <c r="L110" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M110" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="N110" t="inlineStr">
+        <is>
+          <t>I want something I can wear every day</t>
+        </is>
+      </c>
+      <c r="O110" t="inlineStr">
+        <is>
+          <t>SUITABILITY</t>
+        </is>
+      </c>
+      <c r="P110" t="inlineStr">
+        <is>
+          <t>SUNSCREEN_SUITABILITY</t>
+        </is>
+      </c>
+      <c r="Q110" t="inlineStr">
+        <is>
+          <t>SUITABILITY</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>NEW100</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>Synthetic Test</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>I keep this saved because the product looks promising for dry skin, but I am checking whether it layers well with makeup.</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>Skincare</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>WAITING_FOR_BETTER_VALUE</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>['PRICE_VALUE']</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>['PRICE_VALUE']</t>
+        </is>
+      </c>
+      <c r="H111" t="b">
+        <v>0</v>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>['NONE']</t>
+        </is>
+      </c>
+      <c r="J111" t="inlineStr">
+        <is>
+          <t>['NONE']</t>
+        </is>
+      </c>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>['LOWER_PRICE']</t>
+        </is>
+      </c>
+      <c r="L111" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M111" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="N111" t="inlineStr">
+        <is>
+          <t>I keep this saved because the product looks promising for dry skin</t>
+        </is>
+      </c>
+      <c r="O111" t="inlineStr">
+        <is>
+          <t>PRICE_VALUE</t>
+        </is>
+      </c>
+      <c r="P111" t="inlineStr">
+        <is>
+          <t>SKINCARE_PRICE_VALUE</t>
+        </is>
+      </c>
+      <c r="Q111" t="inlineStr">
+        <is>
+          <t>PRICE_VALUE</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:Q11"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -6204,207 +14982,197 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H7"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="19" customWidth="1" min="1" max="1"/>
-    <col width="17" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="24" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
-    <col width="17" customWidth="1" min="6" max="6"/>
-    <col width="19" customWidth="1" min="7" max="7"/>
-    <col width="34" customWidth="1" min="8" max="8"/>
-  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="6" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>opportunity_theme</t>
         </is>
       </c>
-      <c r="B1" s="6" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>frequency_count</t>
         </is>
       </c>
-      <c r="C1" s="6" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>frequency_pct</t>
         </is>
       </c>
-      <c r="D1" s="6" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>purchase_relevance_1_5</t>
         </is>
       </c>
-      <c r="E1" s="6" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>segment_impact_1_5</t>
         </is>
       </c>
-      <c r="F1" s="6" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>solvability_1_5</t>
         </is>
       </c>
-      <c r="G1" s="6" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>opportunity_score</t>
         </is>
       </c>
-      <c r="H1" s="6" t="inlineStr">
-        <is>
-          <t>evidence_notes</t>
-        </is>
-      </c>
     </row>
     <row r="2">
-      <c r="A2" s="4" t="inlineStr">
+      <c r="A2" t="inlineStr">
         <is>
           <t>PRICE_VALUE</t>
         </is>
       </c>
-      <c r="B2" s="4" t="inlineStr"/>
-      <c r="C2" s="4" t="inlineStr"/>
-      <c r="D2" s="4" t="n">
+      <c r="B2" t="n">
+        <v>1206</v>
+      </c>
+      <c r="C2" t="n">
+        <v>47.28</v>
+      </c>
+      <c r="D2" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="E2" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="F2" t="n">
         <v>4</v>
       </c>
-      <c r="E2" s="4" t="n">
+      <c r="G2" t="n">
+        <v>381.23</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>COMPARISON</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>694</v>
+      </c>
+      <c r="C3" t="n">
+        <v>27.21</v>
+      </c>
+      <c r="D3" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="E3" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="F3" t="n">
         <v>4</v>
       </c>
-      <c r="F2" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="G2" s="4" t="inlineStr"/>
-      <c r="H2" s="4" t="inlineStr">
-        <is>
-          <t>Populate from AI classifications</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="4" t="inlineStr">
+      <c r="G3" t="n">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
         <is>
           <t>SHADE_CONFIDENCE</t>
         </is>
       </c>
-      <c r="B3" s="4" t="inlineStr"/>
-      <c r="C3" s="4" t="inlineStr"/>
-      <c r="D3" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="E3" s="4" t="n">
+      <c r="B4" t="n">
+        <v>390</v>
+      </c>
+      <c r="C4" t="n">
+        <v>15.29</v>
+      </c>
+      <c r="D4" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="E4" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="F4" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="G4" t="n">
+        <v>148.6</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>SUITABILITY</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>159</v>
+      </c>
+      <c r="C5" t="n">
+        <v>6.23</v>
+      </c>
+      <c r="D5" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="E5" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="F5" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="G5" t="n">
+        <v>51.78</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>QUALITY_TRUST</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>100</v>
+      </c>
+      <c r="C6" t="n">
+        <v>3.92</v>
+      </c>
+      <c r="D6" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="E6" t="n">
         <v>4</v>
       </c>
-      <c r="F3" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="G3" s="4" t="inlineStr"/>
-      <c r="H3" s="4" t="inlineStr">
-        <is>
-          <t>Populate from AI classifications</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="4" t="inlineStr">
-        <is>
-          <t>SUITABILITY</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="inlineStr"/>
-      <c r="C4" s="4" t="inlineStr"/>
-      <c r="D4" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="E4" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="F4" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="G4" s="4" t="inlineStr"/>
-      <c r="H4" s="4" t="inlineStr">
-        <is>
-          <t>Populate from AI classifications</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t>COMPARISON</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="inlineStr"/>
-      <c r="C5" s="4" t="inlineStr"/>
-      <c r="D5" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="E5" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="F5" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="G5" s="4" t="inlineStr"/>
-      <c r="H5" s="4" t="inlineStr">
-        <is>
-          <t>Populate from AI classifications</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t>QUALITY_TRUST</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="inlineStr"/>
-      <c r="C6" s="4" t="inlineStr"/>
-      <c r="D6" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="E6" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="F6" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="G6" s="4" t="inlineStr"/>
-      <c r="H6" s="4" t="inlineStr">
-        <is>
-          <t>Populate from AI classifications</t>
-        </is>
+      <c r="F6" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="G6" t="n">
+        <v>26.22</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr">
+      <c r="A7" t="inlineStr">
         <is>
           <t>INTENT_DECAY</t>
         </is>
       </c>
-      <c r="B7" s="4" t="inlineStr"/>
-      <c r="C7" s="4" t="inlineStr"/>
-      <c r="D7" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="E7" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="F7" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="G7" s="4" t="inlineStr"/>
-      <c r="H7" s="4" t="inlineStr">
-        <is>
-          <t>Populate from AI classifications</t>
-        </is>
+      <c r="B7" t="n">
+        <v>2</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="D7" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="E7" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="F7" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.48</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H7"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
